--- a/test/integration/rotor/02.xlsx
+++ b/test/integration/rotor/02.xlsx
@@ -1,1073 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Optimizasyon Projesi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="objective" sheetId="1" r:id="rId1"/>
     <sheet name="constraints" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="347">
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Coefficient</t>
-  </si>
-  <si>
-    <t>Buğday, Durum Buğdayı Hariç</t>
-  </si>
-  <si>
-    <t>Buğday, Durum Buğdayı Hariç Satış</t>
-  </si>
-  <si>
-    <t>Buğday (Sulu)</t>
-  </si>
-  <si>
-    <t>Buğday (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Mısır (Dane)</t>
-  </si>
-  <si>
-    <t>Mısır (Dane) Satış</t>
-  </si>
-  <si>
-    <t>Arpa (Diğer) (Kuru)</t>
-  </si>
-  <si>
-    <t>Arpa (Diğer) (Kuru) Satış</t>
-  </si>
-  <si>
-    <t>Arpa (Sulu)</t>
-  </si>
-  <si>
-    <t>Arpa (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Yulaf</t>
-  </si>
-  <si>
-    <t>Yulaf Satış</t>
-  </si>
-  <si>
-    <t>Yulaf (Yeşilot)</t>
-  </si>
-  <si>
-    <t>Yulaf (Yeşilot) Satış</t>
-  </si>
-  <si>
-    <t>Triticale</t>
-  </si>
-  <si>
-    <t>Triticale Satış</t>
-  </si>
-  <si>
-    <t>Triticale (Yeşilot)</t>
-  </si>
-  <si>
-    <t>Triticale (Yeşilot) Satış</t>
-  </si>
-  <si>
-    <t>Fasulye, Taze</t>
-  </si>
-  <si>
-    <t>Fasulye, Taze Satış</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık)</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) Satış</t>
-  </si>
-  <si>
-    <t>Kenevir Tohumu</t>
-  </si>
-  <si>
-    <t>Kenevir Tohumu Satış</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu Satış</t>
-  </si>
-  <si>
-    <t>Şeker Pancarı</t>
-  </si>
-  <si>
-    <t>Şeker Pancarı Satış</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) (Yeşil Ot)</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) (Yeşil Ot) Satış</t>
-  </si>
-  <si>
-    <t>Korunga (Yeşilot)</t>
-  </si>
-  <si>
-    <t>Korunga (Yeşilot) Satış</t>
-  </si>
-  <si>
-    <t>Sorgum (Yeşilot)</t>
-  </si>
-  <si>
-    <t>Sorgum (Yeşilot) Satış</t>
-  </si>
-  <si>
-    <t>Mısır (Slaj)</t>
-  </si>
-  <si>
-    <t>Mısır (Slaj) Satış</t>
-  </si>
-  <si>
-    <t>Çayır Otu (Yeşilot)</t>
-  </si>
-  <si>
-    <t>Çayır Otu (Yeşilot) Satış</t>
-  </si>
-  <si>
-    <t>Bezelye (Yemlik)</t>
-  </si>
-  <si>
-    <t>Bezelye (Yemlik) Satış</t>
-  </si>
-  <si>
-    <t>İtalyan Çimi (Yemlik)</t>
-  </si>
-  <si>
-    <t>İtalyan Çimi (Yemlik) Satış</t>
-  </si>
-  <si>
-    <t>Lavanta</t>
-  </si>
-  <si>
-    <t>Lavanta Satış</t>
-  </si>
-  <si>
-    <t>Barbunya, Taze</t>
-  </si>
-  <si>
-    <t>Barbunya, Taze Satış</t>
-  </si>
-  <si>
-    <t>Lahana (Beyaz)</t>
-  </si>
-  <si>
-    <t>Lahana (Beyaz) Satış</t>
-  </si>
-  <si>
-    <t>Marul (Göbekli)</t>
-  </si>
-  <si>
-    <t>Marul (Göbekli) Satış</t>
-  </si>
-  <si>
-    <t>Ispanak</t>
-  </si>
-  <si>
-    <t>Ispanak Satış</t>
-  </si>
-  <si>
-    <t>Maydanoz</t>
-  </si>
-  <si>
-    <t>Maydanoz Satış</t>
-  </si>
-  <si>
-    <t>Tere</t>
-  </si>
-  <si>
-    <t>Tere Satış</t>
-  </si>
-  <si>
-    <t>Nane</t>
-  </si>
-  <si>
-    <t>Nane Satış</t>
-  </si>
-  <si>
-    <t>Karpuz</t>
-  </si>
-  <si>
-    <t>Karpuz Satış</t>
-  </si>
-  <si>
-    <t>Kavun</t>
-  </si>
-  <si>
-    <t>Kavun Satış</t>
-  </si>
-  <si>
-    <t>Biber (Sivri)</t>
-  </si>
-  <si>
-    <t>Biber (Sivri) Satış</t>
-  </si>
-  <si>
-    <t>Hıyar (Sofralık)</t>
-  </si>
-  <si>
-    <t>Hıyar (Sofralık) Satış</t>
-  </si>
-  <si>
-    <t>Patlıcan</t>
-  </si>
-  <si>
-    <t>Patlıcan Satış</t>
-  </si>
-  <si>
-    <t>Domates (Sofralık)</t>
-  </si>
-  <si>
-    <t>Domates (Sofralık) Satış</t>
-  </si>
-  <si>
-    <t>Havuç</t>
-  </si>
-  <si>
-    <t>Havuç Satış</t>
-  </si>
-  <si>
-    <t>Sarımsak (Kuru)</t>
-  </si>
-  <si>
-    <t>Sarımsak (Kuru) Satış</t>
-  </si>
-  <si>
-    <t>Sarımsak (Taze)</t>
-  </si>
-  <si>
-    <t>Sarımsak (Taze) Satış</t>
-  </si>
-  <si>
-    <t>Soğan (Kuru)</t>
-  </si>
-  <si>
-    <t>Soğan (Kuru) Satış</t>
-  </si>
-  <si>
-    <t>Soğan (Taze)</t>
-  </si>
-  <si>
-    <t>Soğan (Taze) Satış</t>
-  </si>
-  <si>
-    <t>Pırasa</t>
-  </si>
-  <si>
-    <t>Pırasa Satış</t>
-  </si>
-  <si>
-    <t>Turp (Beyaz)</t>
-  </si>
-  <si>
-    <t>Turp (Beyaz) Satış</t>
-  </si>
-  <si>
-    <t>Elma (Bütünleştirilmiş)</t>
-  </si>
-  <si>
-    <t>Elma (Bütünleştirilmiş) Satış</t>
-  </si>
-  <si>
-    <t>Armut</t>
-  </si>
-  <si>
-    <t>Armut Satış</t>
-  </si>
-  <si>
-    <t>Ayva</t>
-  </si>
-  <si>
-    <t>Ayva Satış</t>
-  </si>
-  <si>
-    <t>Kiraz</t>
-  </si>
-  <si>
-    <t>Kiraz Satış</t>
-  </si>
-  <si>
-    <t>Vişne</t>
-  </si>
-  <si>
-    <t>Vişne Satış</t>
-  </si>
-  <si>
-    <t>Şeftali</t>
-  </si>
-  <si>
-    <t>Şeftali Satış</t>
-  </si>
-  <si>
-    <t>Çilek</t>
-  </si>
-  <si>
-    <t>Çilek Satış</t>
-  </si>
-  <si>
-    <t>Erik</t>
-  </si>
-  <si>
-    <t>Erik Satış</t>
-  </si>
-  <si>
-    <t>Ceviz</t>
-  </si>
-  <si>
-    <t>Ceviz Satış</t>
-  </si>
-  <si>
-    <t>Çörek Otu Tohumu</t>
-  </si>
-  <si>
-    <t>Çörek Otu Tohumu Satış</t>
-  </si>
-  <si>
-    <t>Mantar (Kültür)</t>
-  </si>
-  <si>
-    <t>Mantar (Kültür) Satış</t>
-  </si>
-  <si>
-    <t>Acur</t>
-  </si>
-  <si>
-    <t>Acur Satış</t>
-  </si>
-  <si>
-    <t>Badem</t>
-  </si>
-  <si>
-    <t>Badem Satış</t>
-  </si>
-  <si>
-    <t>Buy (Çemen Otu)</t>
-  </si>
-  <si>
-    <t>Buy (Çemen Otu) Satış</t>
-  </si>
-  <si>
-    <t>Çavdar</t>
-  </si>
-  <si>
-    <t>Çavdar Satış</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) Tohumu</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) Tohumu Satış</t>
-  </si>
-  <si>
-    <t>Kabak (Çerezlik)</t>
-  </si>
-  <si>
-    <t>Kabak (Çerezlik) Satış</t>
-  </si>
-  <si>
-    <t>Kayısı</t>
-  </si>
-  <si>
-    <t>Kayısı Satış</t>
-  </si>
-  <si>
-    <t>Kimyon, İşlenmemiş</t>
-  </si>
-  <si>
-    <t>Kimyon, İşlenmemiş Satış</t>
-  </si>
-  <si>
-    <t>Mercimek, Kuru (Yeşil)</t>
-  </si>
-  <si>
-    <t>Mercimek, Kuru (Yeşil) Satış</t>
-  </si>
-  <si>
-    <t>Nohut, Kuru</t>
-  </si>
-  <si>
-    <t>Nohut, Kuru Satış</t>
-  </si>
-  <si>
-    <t>Sofralık Üzüm, Çekirdekli</t>
-  </si>
-  <si>
-    <t>Sofralık Üzüm, Çekirdekli Satış</t>
-  </si>
-  <si>
-    <t>Sorgum</t>
-  </si>
-  <si>
-    <t>Sorgum Satış</t>
-  </si>
-  <si>
-    <t>Tatlı Patates</t>
-  </si>
-  <si>
-    <t>Tatlı Patates Satış</t>
-  </si>
-  <si>
-    <t>Yonca Tohumu</t>
-  </si>
-  <si>
-    <t>Yonca Tohumu Satış</t>
-  </si>
-  <si>
-    <t>Zerdali</t>
-  </si>
-  <si>
-    <t>Zerdali Satış</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu (Sulu)</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) (Sulu)</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Fasulye (Kuru)</t>
-  </si>
-  <si>
-    <t>Fasulye (Kuru) Satış</t>
-  </si>
-  <si>
-    <t>Triticale (Sulu)</t>
-  </si>
-  <si>
-    <t>Triticale (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Mercimek, Sulu (Yeşil)</t>
-  </si>
-  <si>
-    <t>Mercimek, Sulu (Yeşil) Satış</t>
-  </si>
-  <si>
-    <t>Fasulye, Kuru (Sulu)</t>
-  </si>
-  <si>
-    <t>Fasulye, Kuru (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Yulaf (Sulu)</t>
-  </si>
-  <si>
-    <t>Yulaf (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>Nohut (Sulu)</t>
-  </si>
-  <si>
-    <t>Nohut (Sulu) Satış</t>
-  </si>
-  <si>
-    <t>İg1</t>
-  </si>
-  <si>
-    <t>İg2</t>
-  </si>
-  <si>
-    <t>İg3</t>
-  </si>
-  <si>
-    <t>İg4</t>
-  </si>
-  <si>
-    <t>İg5</t>
-  </si>
-  <si>
-    <t>İg6</t>
-  </si>
-  <si>
-    <t>İg7</t>
-  </si>
-  <si>
-    <t>İg8</t>
-  </si>
-  <si>
-    <t>İg9</t>
-  </si>
-  <si>
-    <t>İg10</t>
-  </si>
-  <si>
-    <t>İg11</t>
-  </si>
-  <si>
-    <t>İg12</t>
-  </si>
-  <si>
-    <t>Sermaye Temini</t>
-  </si>
-  <si>
-    <t>Süt sığırcılığı</t>
-  </si>
-  <si>
-    <t>Koyunculuk</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Relation</t>
-  </si>
-  <si>
-    <t>RHS</t>
-  </si>
-  <si>
-    <t>Toplam Arazi</t>
-  </si>
-  <si>
-    <t>&lt;=</t>
-  </si>
-  <si>
-    <t>Toplam Kuru Tarla Arazisi</t>
-  </si>
-  <si>
-    <t>Toplam Sulu Tarla Arazisi</t>
-  </si>
-  <si>
-    <t>Toplam Meyve Arazisi</t>
-  </si>
-  <si>
-    <t>Toplam Sebze Arazisi</t>
-  </si>
-  <si>
-    <t>Toplam Örtü Altı Arazisi</t>
-  </si>
-  <si>
-    <t>Toplam Süs Bitkisi Arazisi</t>
-  </si>
-  <si>
-    <t>Buğday, Durum Buğdayı Hariç Arazisi</t>
-  </si>
-  <si>
-    <t>Buğday (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Mısır (Dane) Arazisi</t>
-  </si>
-  <si>
-    <t>Arpa (Diğer) (Kuru) Arazisi</t>
-  </si>
-  <si>
-    <t>Arpa (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Yulaf Arazisi</t>
-  </si>
-  <si>
-    <t>Yulaf (Yeşilot) Arazisi</t>
-  </si>
-  <si>
-    <t>Triticale Arazisi</t>
-  </si>
-  <si>
-    <t>Triticale (Yeşilot) Arazisi</t>
-  </si>
-  <si>
-    <t>Fasulye, Taze Arazisi</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) Arazisi</t>
-  </si>
-  <si>
-    <t>Kenevir Tohumu Arazisi</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu Arazisi</t>
-  </si>
-  <si>
-    <t>Şeker Pancarı Arazisi</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) (Yeşil Ot) Arazisi</t>
-  </si>
-  <si>
-    <t>Korunga (Yeşilot) Arazisi</t>
-  </si>
-  <si>
-    <t>Sorgum (Yeşilot) Arazisi</t>
-  </si>
-  <si>
-    <t>Mısır (Slaj) Arazisi</t>
-  </si>
-  <si>
-    <t>Çayır Otu (Yeşilot) Arazisi</t>
-  </si>
-  <si>
-    <t>Bezelye (Yemlik) Arazisi</t>
-  </si>
-  <si>
-    <t>İtalyan Çimi (Yemlik) Arazisi</t>
-  </si>
-  <si>
-    <t>Lavanta Arazisi</t>
-  </si>
-  <si>
-    <t>Barbunya, Taze Arazisi</t>
-  </si>
-  <si>
-    <t>Lahana (Beyaz) Arazisi</t>
-  </si>
-  <si>
-    <t>Marul (Göbekli) Arazisi</t>
-  </si>
-  <si>
-    <t>Ispanak Arazisi</t>
-  </si>
-  <si>
-    <t>Maydanoz Arazisi</t>
-  </si>
-  <si>
-    <t>Tere Arazisi</t>
-  </si>
-  <si>
-    <t>Nane Arazisi</t>
-  </si>
-  <si>
-    <t>Karpuz Arazisi</t>
-  </si>
-  <si>
-    <t>Kavun Arazisi</t>
-  </si>
-  <si>
-    <t>Biber (Sivri) Arazisi</t>
-  </si>
-  <si>
-    <t>Hıyar (Sofralık) Arazisi</t>
-  </si>
-  <si>
-    <t>Patlıcan Arazisi</t>
-  </si>
-  <si>
-    <t>Domates (Sofralık) Arazisi</t>
-  </si>
-  <si>
-    <t>Havuç Arazisi</t>
-  </si>
-  <si>
-    <t>Sarımsak (Kuru) Arazisi</t>
-  </si>
-  <si>
-    <t>Sarımsak (Taze) Arazisi</t>
-  </si>
-  <si>
-    <t>Soğan (Kuru) Arazisi</t>
-  </si>
-  <si>
-    <t>Soğan (Taze) Arazisi</t>
-  </si>
-  <si>
-    <t>Pırasa Arazisi</t>
-  </si>
-  <si>
-    <t>Turp (Beyaz) Arazisi</t>
-  </si>
-  <si>
-    <t>Elma (Bütünleştirilmiş) Arazisi</t>
-  </si>
-  <si>
-    <t>Armut Arazisi</t>
-  </si>
-  <si>
-    <t>Ayva Arazisi</t>
-  </si>
-  <si>
-    <t>Kiraz Arazisi</t>
-  </si>
-  <si>
-    <t>Vişne Arazisi</t>
-  </si>
-  <si>
-    <t>Şeftali Arazisi</t>
-  </si>
-  <si>
-    <t>Çilek Arazisi</t>
-  </si>
-  <si>
-    <t>Erik Arazisi</t>
-  </si>
-  <si>
-    <t>Ceviz Arazisi</t>
-  </si>
-  <si>
-    <t>Çörek Otu Tohumu Arazisi</t>
-  </si>
-  <si>
-    <t>Mantar (Kültür) Arazisi</t>
-  </si>
-  <si>
-    <t>Acur Arazisi</t>
-  </si>
-  <si>
-    <t>Badem Arazisi</t>
-  </si>
-  <si>
-    <t>Buy (Çemen Otu) Arazisi</t>
-  </si>
-  <si>
-    <t>Çavdar Arazisi</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) Tohumu Arazisi</t>
-  </si>
-  <si>
-    <t>Kabak (Çerezlik) Arazisi</t>
-  </si>
-  <si>
-    <t>Kayısı Arazisi</t>
-  </si>
-  <si>
-    <t>Kimyon, İşlenmemiş Arazisi</t>
-  </si>
-  <si>
-    <t>Mercimek, Kuru (Yeşil) Arazisi</t>
-  </si>
-  <si>
-    <t>Nohut, Kuru Arazisi</t>
-  </si>
-  <si>
-    <t>Sofralık Üzüm, Çekirdekli Arazisi</t>
-  </si>
-  <si>
-    <t>Sorgum Arazisi</t>
-  </si>
-  <si>
-    <t>Tatlı Patates Arazisi</t>
-  </si>
-  <si>
-    <t>Yonca Tohumu Arazisi</t>
-  </si>
-  <si>
-    <t>Zerdali Arazisi</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Fasulye (Kuru) Arazisi</t>
-  </si>
-  <si>
-    <t>Triticale (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Mercimek, Sulu (Yeşil) Arazisi</t>
-  </si>
-  <si>
-    <t>Fasulye, Kuru (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Yulaf (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Nohut (Sulu) Arazisi</t>
-  </si>
-  <si>
-    <t>Buğday, Durum Buğdayı Hariç Transfer</t>
-  </si>
-  <si>
-    <t>Buğday (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Mısır (Dane) Transfer</t>
-  </si>
-  <si>
-    <t>Arpa (Diğer) (Kuru) Transfer</t>
-  </si>
-  <si>
-    <t>Arpa (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Yulaf Transfer</t>
-  </si>
-  <si>
-    <t>Yulaf (Yeşilot) Transfer</t>
-  </si>
-  <si>
-    <t>Triticale Transfer</t>
-  </si>
-  <si>
-    <t>Triticale (Yeşilot) Transfer</t>
-  </si>
-  <si>
-    <t>Fasulye, Taze Transfer</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) Transfer</t>
-  </si>
-  <si>
-    <t>Kenevir Tohumu Transfer</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu Transfer</t>
-  </si>
-  <si>
-    <t>Şeker Pancarı Transfer</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) (Yeşil Ot) Transfer</t>
-  </si>
-  <si>
-    <t>Korunga (Yeşilot) Transfer</t>
-  </si>
-  <si>
-    <t>Sorgum (Yeşilot) Transfer</t>
-  </si>
-  <si>
-    <t>Mısır (Slaj) Transfer</t>
-  </si>
-  <si>
-    <t>Çayır Otu (Yeşilot) Transfer</t>
-  </si>
-  <si>
-    <t>Bezelye (Yemlik) Transfer</t>
-  </si>
-  <si>
-    <t>İtalyan Çimi (Yemlik) Transfer</t>
-  </si>
-  <si>
-    <t>Lavanta Transfer</t>
-  </si>
-  <si>
-    <t>Barbunya, Taze Transfer</t>
-  </si>
-  <si>
-    <t>Lahana (Beyaz) Transfer</t>
-  </si>
-  <si>
-    <t>Marul (Göbekli) Transfer</t>
-  </si>
-  <si>
-    <t>Ispanak Transfer</t>
-  </si>
-  <si>
-    <t>Maydanoz Transfer</t>
-  </si>
-  <si>
-    <t>Tere Transfer</t>
-  </si>
-  <si>
-    <t>Nane Transfer</t>
-  </si>
-  <si>
-    <t>Karpuz Transfer</t>
-  </si>
-  <si>
-    <t>Kavun Transfer</t>
-  </si>
-  <si>
-    <t>Biber (Sivri) Transfer</t>
-  </si>
-  <si>
-    <t>Hıyar (Sofralık) Transfer</t>
-  </si>
-  <si>
-    <t>Patlıcan Transfer</t>
-  </si>
-  <si>
-    <t>Domates (Sofralık) Transfer</t>
-  </si>
-  <si>
-    <t>Havuç Transfer</t>
-  </si>
-  <si>
-    <t>Sarımsak (Kuru) Transfer</t>
-  </si>
-  <si>
-    <t>Sarımsak (Taze) Transfer</t>
-  </si>
-  <si>
-    <t>Soğan (Kuru) Transfer</t>
-  </si>
-  <si>
-    <t>Soğan (Taze) Transfer</t>
-  </si>
-  <si>
-    <t>Pırasa Transfer</t>
-  </si>
-  <si>
-    <t>Turp (Beyaz) Transfer</t>
-  </si>
-  <si>
-    <t>Elma (Bütünleştirilmiş) Transfer</t>
-  </si>
-  <si>
-    <t>Armut Transfer</t>
-  </si>
-  <si>
-    <t>Ayva Transfer</t>
-  </si>
-  <si>
-    <t>Kiraz Transfer</t>
-  </si>
-  <si>
-    <t>Vişne Transfer</t>
-  </si>
-  <si>
-    <t>Şeftali Transfer</t>
-  </si>
-  <si>
-    <t>Çilek Transfer</t>
-  </si>
-  <si>
-    <t>Erik Transfer</t>
-  </si>
-  <si>
-    <t>Ceviz Transfer</t>
-  </si>
-  <si>
-    <t>Çörek Otu Tohumu Transfer</t>
-  </si>
-  <si>
-    <t>Mantar (Kültür) Transfer</t>
-  </si>
-  <si>
-    <t>Acur Transfer</t>
-  </si>
-  <si>
-    <t>Badem Transfer</t>
-  </si>
-  <si>
-    <t>Buy (Çemen Otu) Transfer</t>
-  </si>
-  <si>
-    <t>Çavdar Transfer</t>
-  </si>
-  <si>
-    <t>Fiğ (Adi) Tohumu Transfer</t>
-  </si>
-  <si>
-    <t>Kabak (Çerezlik) Transfer</t>
-  </si>
-  <si>
-    <t>Kayısı Transfer</t>
-  </si>
-  <si>
-    <t>Kimyon, İşlenmemiş Transfer</t>
-  </si>
-  <si>
-    <t>Mercimek, Kuru (Yeşil) Transfer</t>
-  </si>
-  <si>
-    <t>Nohut, Kuru Transfer</t>
-  </si>
-  <si>
-    <t>Sofralık Üzüm, Çekirdekli Transfer</t>
-  </si>
-  <si>
-    <t>Sorgum Transfer</t>
-  </si>
-  <si>
-    <t>Tatlı Patates Transfer</t>
-  </si>
-  <si>
-    <t>Yonca Tohumu Transfer</t>
-  </si>
-  <si>
-    <t>Zerdali Transfer</t>
-  </si>
-  <si>
-    <t>Aspir Tohumu (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Fasulye (Kuru) Transfer</t>
-  </si>
-  <si>
-    <t>Triticale (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Mercimek, Sulu (Yeşil) Transfer</t>
-  </si>
-  <si>
-    <t>Fasulye, Kuru (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Yulaf (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>Nohut (Sulu) Transfer</t>
-  </si>
-  <si>
-    <t>İşgücü Ocak</t>
-  </si>
-  <si>
-    <t>İşgücü Şubat</t>
-  </si>
-  <si>
-    <t>İşgücü Mart</t>
-  </si>
-  <si>
-    <t>İşgücü Nisan</t>
-  </si>
-  <si>
-    <t>İşgücü Mayıs</t>
-  </si>
-  <si>
-    <t>İşgücü Haziran</t>
-  </si>
-  <si>
-    <t>İşgücü Temmuz</t>
-  </si>
-  <si>
-    <t>İşgücü Ağustos</t>
-  </si>
-  <si>
-    <t>İşgücü Eylül</t>
-  </si>
-  <si>
-    <t>İşgücü Ekim</t>
-  </si>
-  <si>
-    <t>İşgücü Kasım</t>
-  </si>
-  <si>
-    <t>İşgücü Aralık</t>
-  </si>
-  <si>
-    <t>İşletme Sermayesi</t>
-  </si>
-  <si>
-    <t>Ahır Yeri</t>
-  </si>
-  <si>
-    <t>Ağıl Yeri</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1075,35 +24,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1111,51 +41,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1197,7 +99,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1229,10 +131,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1264,7 +165,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1440,2066 +340,2742 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B168"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coefficient</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç</t>
+        </is>
       </c>
       <c r="B2">
         <v>-324.12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç Satış</t>
+        </is>
       </c>
       <c r="B3">
         <v>2.73</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu)</t>
+        </is>
+      </c>
+      <c r="B4">
         <v>-839.12</v>
       </c>
-      <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mısır (Dane)</t>
+        </is>
       </c>
       <c r="B6">
         <v>-1439.82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mısır (Dane) Satış</t>
+        </is>
       </c>
       <c r="B7">
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru)</t>
+        </is>
       </c>
       <c r="B8">
         <v>-292.92</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>9</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru) Satış</t>
+        </is>
       </c>
       <c r="B9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu)</t>
+        </is>
       </c>
       <c r="B10">
         <v>-721.12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>12</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Yulaf</t>
+        </is>
       </c>
       <c r="B12">
         <v>-253.62</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>13</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yulaf Satış</t>
+        </is>
       </c>
       <c r="B13">
         <v>2.63</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>14</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot)</t>
+        </is>
       </c>
       <c r="B14">
         <v>-245.55</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot) Satış</t>
+        </is>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>16</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triticale</t>
+        </is>
       </c>
       <c r="B16">
         <v>-311.42</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>17</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triticale Satış</t>
+        </is>
       </c>
       <c r="B17">
         <v>2.35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>18</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot)</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-923.56</v>
+        <v>-923.5599999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>19</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot) Satış</t>
+        </is>
       </c>
       <c r="B19">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze</t>
+        </is>
       </c>
       <c r="B20">
         <v>-1935.27</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>21</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze Satış</t>
+        </is>
       </c>
       <c r="B21">
         <v>2.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık)</t>
+        </is>
       </c>
       <c r="B22">
         <v>-522.39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) Satış</t>
+        </is>
       </c>
       <c r="B23">
         <v>5.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu</t>
+        </is>
       </c>
       <c r="B24">
         <v>-1022.54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>25</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu Satış</t>
+        </is>
       </c>
       <c r="B25">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>26</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu</t>
+        </is>
       </c>
       <c r="B26">
         <v>-139.4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>27</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu Satış</t>
+        </is>
       </c>
       <c r="B27">
         <v>1.3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>28</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı</t>
+        </is>
       </c>
       <c r="B28">
         <v>-2035.67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>29</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı Satış</t>
+        </is>
       </c>
       <c r="B29">
         <v>0.48</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>30</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot)</t>
+        </is>
       </c>
       <c r="B30">
         <v>-469.64</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>31</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot) Satış</t>
+        </is>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>32</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot)</t>
+        </is>
       </c>
       <c r="B32">
         <v>-426</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>33</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot) Satış</t>
+        </is>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>34</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot)</t>
+        </is>
       </c>
       <c r="B34">
         <v>-458.96</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>35</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot) Satış</t>
+        </is>
       </c>
       <c r="B35">
         <v>0.3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>36</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj)</t>
+        </is>
       </c>
       <c r="B36">
         <v>-1323.15</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>37</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj) Satış</t>
+        </is>
       </c>
       <c r="B37">
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>38</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot)</t>
+        </is>
       </c>
       <c r="B38">
         <v>-235.45</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>39</v>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot) Satış</t>
+        </is>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>40</v>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik)</t>
+        </is>
       </c>
       <c r="B40">
         <v>-704.35</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>41</v>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik) Satış</t>
+        </is>
       </c>
       <c r="B41">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>42</v>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik)</t>
+        </is>
       </c>
       <c r="B42">
         <v>-1542.22</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>43</v>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik) Satış</t>
+        </is>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>44</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lavanta</t>
+        </is>
       </c>
       <c r="B44">
         <v>-2062.33</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>45</v>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lavanta Satış</t>
+        </is>
       </c>
       <c r="B45">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>46</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze</t>
+        </is>
       </c>
       <c r="B46">
         <v>-1524.22</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>47</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze Satış</t>
+        </is>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>48</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz)</t>
+        </is>
       </c>
       <c r="B48">
         <v>-4731.46</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>49</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz) Satış</t>
+        </is>
       </c>
       <c r="B49">
         <v>1.24</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>50</v>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli)</t>
+        </is>
       </c>
       <c r="B50">
-        <v>-4564.1400000000003</v>
+        <v>-4564.14</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>51</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli) Satış</t>
+        </is>
       </c>
       <c r="B51">
         <v>1.4</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>52</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ispanak</t>
+        </is>
       </c>
       <c r="B52">
         <v>-2800.16</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>53</v>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ispanak Satış</t>
+        </is>
       </c>
       <c r="B53">
         <v>4.75</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>54</v>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Maydanoz</t>
+        </is>
       </c>
       <c r="B54">
         <v>-1201.23</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>55</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Maydanoz Satış</t>
+        </is>
       </c>
       <c r="B55">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>56</v>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tere</t>
+        </is>
       </c>
       <c r="B56">
         <v>-1012.14</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>57</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Tere Satış</t>
+        </is>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>58</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nane</t>
+        </is>
       </c>
       <c r="B58">
         <v>-2546.56</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>59</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nane Satış</t>
+        </is>
       </c>
       <c r="B59">
         <v>4.33</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>60</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Karpuz</t>
+        </is>
       </c>
       <c r="B60">
         <v>-2710.05</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>61</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Karpuz Satış</t>
+        </is>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>62</v>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Kavun</t>
+        </is>
       </c>
       <c r="B62">
-        <v>-2166.6799999999998</v>
+        <v>-2166.68</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>63</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kavun Satış</t>
+        </is>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>64</v>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Biber (Sivri)</t>
+        </is>
       </c>
       <c r="B64">
-        <v>-8502.9500000000007</v>
+        <v>-8502.950000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>65</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Biber (Sivri) Satış</t>
+        </is>
       </c>
       <c r="B65">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>66</v>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık)</t>
+        </is>
       </c>
       <c r="B66">
         <v>-5892.95</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>67</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık) Satış</t>
+        </is>
       </c>
       <c r="B67">
         <v>2.6</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>68</v>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Patlıcan</t>
+        </is>
       </c>
       <c r="B68">
         <v>-7597.45</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>69</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Patlıcan Satış</t>
+        </is>
       </c>
       <c r="B69">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>70</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık)</t>
+        </is>
       </c>
       <c r="B70">
         <v>-6173.95</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>71</v>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık) Satış</t>
+        </is>
       </c>
       <c r="B71">
         <v>1.7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>72</v>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Havuç</t>
+        </is>
       </c>
       <c r="B72">
         <v>-1640.96</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>73</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Havuç Satış</t>
+        </is>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>74</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru)</t>
+        </is>
       </c>
       <c r="B74">
         <v>-5458.56</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>75</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru) Satış</t>
+        </is>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>76</v>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze)</t>
+        </is>
       </c>
       <c r="B76">
         <v>-3383.5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>77</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze) Satış</t>
+        </is>
       </c>
       <c r="B77">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>78</v>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru)</t>
+        </is>
       </c>
       <c r="B78">
         <v>-2033.1</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>79</v>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru) Satış</t>
+        </is>
       </c>
       <c r="B79">
         <v>0.7</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>80</v>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Soğan (Taze)</t>
+        </is>
       </c>
       <c r="B80">
         <v>-2619.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>81</v>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Soğan (Taze) Satış</t>
+        </is>
       </c>
       <c r="B81">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>82</v>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pırasa</t>
+        </is>
       </c>
       <c r="B82">
         <v>-3546.89</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>83</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Pırasa Satış</t>
+        </is>
       </c>
       <c r="B83">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>84</v>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz)</t>
+        </is>
       </c>
       <c r="B84">
         <v>-1045.56</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>85</v>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz) Satış</t>
+        </is>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>86</v>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş)</t>
+        </is>
       </c>
       <c r="B86">
         <v>-3040</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>87</v>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş) Satış</t>
+        </is>
       </c>
       <c r="B87">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>88</v>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Armut</t>
+        </is>
       </c>
       <c r="B88">
         <v>-1004.65</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>89</v>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Armut Satış</t>
+        </is>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>90</v>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ayva</t>
+        </is>
       </c>
       <c r="B90">
         <v>-3040</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>91</v>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ayva Satış</t>
+        </is>
       </c>
       <c r="B91">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>92</v>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kiraz</t>
+        </is>
       </c>
       <c r="B92">
         <v>-1346.3</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>93</v>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Kiraz Satış</t>
+        </is>
       </c>
       <c r="B93">
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>94</v>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Vişne</t>
+        </is>
       </c>
       <c r="B94">
         <v>-928.25</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>95</v>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Vişne Satış</t>
+        </is>
       </c>
       <c r="B95">
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>96</v>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Şeftali</t>
+        </is>
       </c>
       <c r="B96">
         <v>-2090</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>97</v>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Şeftali Satış</t>
+        </is>
       </c>
       <c r="B97">
         <v>2.5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>98</v>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Çilek</t>
+        </is>
       </c>
       <c r="B98">
         <v>-7030</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>99</v>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Çilek Satış</t>
+        </is>
       </c>
       <c r="B99">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>100</v>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Erik</t>
+        </is>
       </c>
       <c r="B100">
         <v>-2090</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>101</v>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Erik Satış</t>
+        </is>
       </c>
       <c r="B101">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>102</v>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ceviz</t>
+        </is>
       </c>
       <c r="B102">
         <v>-1514</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>103</v>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ceviz Satış</t>
+        </is>
       </c>
       <c r="B103">
         <v>4.25</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>104</v>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu</t>
+        </is>
       </c>
       <c r="B104">
         <v>-874.66</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>105</v>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu Satış</t>
+        </is>
       </c>
       <c r="B105">
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>106</v>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür)</t>
+        </is>
       </c>
       <c r="B106">
         <v>-1542.23</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>107</v>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür) Satış</t>
+        </is>
       </c>
       <c r="B107">
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>108</v>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Acur</t>
+        </is>
       </c>
       <c r="B108">
         <v>-1524.56</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>109</v>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Acur Satış</t>
+        </is>
       </c>
       <c r="B109">
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>110</v>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Badem</t>
+        </is>
       </c>
       <c r="B110">
         <v>-5720</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>111</v>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Badem Satış</t>
+        </is>
       </c>
       <c r="B111">
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>112</v>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu)</t>
+        </is>
       </c>
       <c r="B112">
         <v>-358.45</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>113</v>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu) Satış</t>
+        </is>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>114</v>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Çavdar</t>
+        </is>
       </c>
       <c r="B114">
         <v>-232.7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>115</v>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Çavdar Satış</t>
+        </is>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>116</v>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu</t>
+        </is>
       </c>
       <c r="B116">
         <v>-408.7</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>117</v>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu Satış</t>
+        </is>
       </c>
       <c r="B117">
         <v>0.6</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>118</v>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik)</t>
+        </is>
       </c>
       <c r="B118">
         <v>-1344.71</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>119</v>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik) Satış</t>
+        </is>
       </c>
       <c r="B119">
         <v>19.5</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>120</v>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Kayısı</t>
+        </is>
       </c>
       <c r="B120">
         <v>-2090</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>121</v>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Kayısı Satış</t>
+        </is>
       </c>
       <c r="B121">
         <v>2.5</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>122</v>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş</t>
+        </is>
       </c>
       <c r="B122">
-        <v>-515.29999999999995</v>
+        <v>-515.3</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>123</v>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş Satış</t>
+        </is>
       </c>
       <c r="B123">
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>124</v>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil)</t>
+        </is>
       </c>
       <c r="B124">
         <v>-364.85</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>125</v>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil) Satış</t>
+        </is>
       </c>
       <c r="B125">
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>126</v>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru</t>
+        </is>
       </c>
       <c r="B126">
         <v>-276.95</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>127</v>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru Satış</t>
+        </is>
       </c>
       <c r="B127">
         <v>6.5</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>128</v>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli</t>
+        </is>
       </c>
       <c r="B128">
         <v>-1834</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>129</v>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli Satış</t>
+        </is>
       </c>
       <c r="B129">
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>130</v>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sorgum</t>
+        </is>
       </c>
       <c r="B130">
         <v>-152.24</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>131</v>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sorgum Satış</t>
+        </is>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>132</v>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Tatlı Patates</t>
+        </is>
       </c>
       <c r="B132">
         <v>-3653.69</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>133</v>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Tatlı Patates Satış</t>
+        </is>
       </c>
       <c r="B133">
         <v>1.2</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>134</v>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu</t>
+        </is>
       </c>
       <c r="B134">
         <v>-982.14</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>135</v>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu Satış</t>
+        </is>
       </c>
       <c r="B135">
         <v>1.6</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>136</v>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Zerdali</t>
+        </is>
       </c>
       <c r="B136">
         <v>-1115.45</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>137</v>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Zerdali Satış</t>
+        </is>
       </c>
       <c r="B137">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>138</v>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu)</t>
+        </is>
       </c>
       <c r="B138">
         <v>-120.25</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>139</v>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B139">
         <v>1.3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>140</v>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu)</t>
+        </is>
       </c>
       <c r="B140">
         <v>-821.15</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>141</v>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B141">
         <v>5.5</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>142</v>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru)</t>
+        </is>
       </c>
       <c r="B142">
         <v>-858.45</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>143</v>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru) Satış</t>
+        </is>
       </c>
       <c r="B143">
-        <v>8.11</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>144</v>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu)</t>
+        </is>
       </c>
       <c r="B144">
         <v>-684.45</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>145</v>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B145">
         <v>2.35</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>146</v>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil)</t>
+        </is>
       </c>
       <c r="B146">
         <v>-450.25</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>147</v>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil) Satış</t>
+        </is>
       </c>
       <c r="B147">
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>148</v>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu)</t>
+        </is>
       </c>
       <c r="B148">
         <v>-1847.87</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>149</v>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B149">
-        <v>8.11</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>150</v>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu)</t>
+        </is>
       </c>
       <c r="B150">
         <v>-678.45</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>151</v>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B151">
         <v>2.63</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>152</v>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu)</t>
+        </is>
       </c>
       <c r="B152">
         <v>-598.9</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>153</v>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu) Satış</t>
+        </is>
       </c>
       <c r="B153">
         <v>6.3</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>154</v>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>İg1</t>
+        </is>
       </c>
       <c r="B154">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>155</v>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>İg2</t>
+        </is>
       </c>
       <c r="B155">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>156</v>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>İg3</t>
+        </is>
       </c>
       <c r="B156">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>157</v>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>İg4</t>
+        </is>
       </c>
       <c r="B157">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>158</v>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>İg5</t>
+        </is>
       </c>
       <c r="B158">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>159</v>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>İg6</t>
+        </is>
       </c>
       <c r="B159">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>160</v>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>İg7</t>
+        </is>
       </c>
       <c r="B160">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>161</v>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>İg8</t>
+        </is>
       </c>
       <c r="B161">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>162</v>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>İg9</t>
+        </is>
       </c>
       <c r="B162">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>163</v>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>İg10</t>
+        </is>
       </c>
       <c r="B163">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>164</v>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>İg11</t>
+        </is>
       </c>
       <c r="B164">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>165</v>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>İg12</t>
+        </is>
       </c>
       <c r="B165">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>166</v>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sermaye Temini</t>
+        </is>
       </c>
       <c r="B166">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>167</v>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Süt sığırcılığı</t>
+        </is>
       </c>
       <c r="B167">
         <v>5014</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>168</v>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Koyunculuk</t>
+        </is>
       </c>
       <c r="B168">
         <v>977</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D170" s="1"/>
-      <c r="E170" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:FN175"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.109375" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" customWidth="1"/>
-    <col min="11" max="11" width="22.88671875" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="13" max="13" width="15.88671875" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
-    <col min="19" max="19" width="14.109375" customWidth="1"/>
-    <col min="20" max="20" width="17.5546875" customWidth="1"/>
-    <col min="21" max="21" width="22.88671875" customWidth="1"/>
-    <col min="22" max="22" width="12.33203125" customWidth="1"/>
-    <col min="23" max="23" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="22.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="18" max="18" width="8.85546875" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
+    <col min="21" max="21" width="22.85546875" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="17.5703125" customWidth="1"/>
     <col min="24" max="24" width="22" customWidth="1"/>
-    <col min="25" max="25" width="27.33203125" customWidth="1"/>
-    <col min="26" max="26" width="13.33203125" customWidth="1"/>
-    <col min="27" max="27" width="18.5546875" customWidth="1"/>
-    <col min="28" max="28" width="11.44140625" customWidth="1"/>
-    <col min="29" max="29" width="16.6640625" customWidth="1"/>
-    <col min="30" max="30" width="12.33203125" customWidth="1"/>
-    <col min="31" max="31" width="17.5546875" customWidth="1"/>
-    <col min="32" max="32" width="18.5546875" customWidth="1"/>
-    <col min="33" max="33" width="23.88671875" customWidth="1"/>
-    <col min="34" max="34" width="15.88671875" customWidth="1"/>
-    <col min="35" max="35" width="21.109375" customWidth="1"/>
+    <col min="25" max="25" width="27.28515625" customWidth="1"/>
+    <col min="26" max="26" width="13.28515625" customWidth="1"/>
+    <col min="27" max="27" width="18.5703125" customWidth="1"/>
+    <col min="28" max="28" width="11.42578125" customWidth="1"/>
+    <col min="29" max="29" width="16.7109375" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" customWidth="1"/>
+    <col min="31" max="31" width="17.5703125" customWidth="1"/>
+    <col min="32" max="32" width="18.5703125" customWidth="1"/>
+    <col min="33" max="33" width="23.85546875" customWidth="1"/>
+    <col min="34" max="34" width="15.85546875" customWidth="1"/>
+    <col min="35" max="35" width="21.140625" customWidth="1"/>
     <col min="36" max="36" width="15" customWidth="1"/>
-    <col min="37" max="37" width="20.33203125" customWidth="1"/>
-    <col min="38" max="38" width="11.44140625" customWidth="1"/>
-    <col min="39" max="39" width="16.6640625" customWidth="1"/>
-    <col min="40" max="40" width="17.5546875" customWidth="1"/>
-    <col min="41" max="41" width="22.88671875" customWidth="1"/>
+    <col min="37" max="37" width="20.28515625" customWidth="1"/>
+    <col min="38" max="38" width="11.42578125" customWidth="1"/>
+    <col min="39" max="39" width="16.7109375" customWidth="1"/>
+    <col min="40" max="40" width="17.5703125" customWidth="1"/>
+    <col min="41" max="41" width="22.85546875" customWidth="1"/>
     <col min="42" max="42" width="15" customWidth="1"/>
-    <col min="43" max="44" width="20.33203125" customWidth="1"/>
-    <col min="45" max="45" width="25.5546875" customWidth="1"/>
-    <col min="46" max="46" width="7.109375" customWidth="1"/>
-    <col min="47" max="47" width="12.33203125" customWidth="1"/>
-    <col min="48" max="48" width="13.33203125" customWidth="1"/>
-    <col min="49" max="49" width="18.5546875" customWidth="1"/>
-    <col min="50" max="50" width="13.33203125" customWidth="1"/>
-    <col min="51" max="51" width="18.5546875" customWidth="1"/>
-    <col min="52" max="52" width="14.109375" customWidth="1"/>
-    <col min="53" max="53" width="19.44140625" customWidth="1"/>
-    <col min="54" max="54" width="7.109375" customWidth="1"/>
-    <col min="55" max="55" width="12.33203125" customWidth="1"/>
+    <col min="43" max="43" width="20.28515625" customWidth="1"/>
+    <col min="44" max="44" width="20.28515625" customWidth="1"/>
+    <col min="45" max="45" width="25.5703125" customWidth="1"/>
+    <col min="46" max="46" width="7.140625" customWidth="1"/>
+    <col min="47" max="47" width="12.28515625" customWidth="1"/>
+    <col min="48" max="48" width="13.28515625" customWidth="1"/>
+    <col min="49" max="49" width="18.5703125" customWidth="1"/>
+    <col min="50" max="50" width="13.28515625" customWidth="1"/>
+    <col min="51" max="51" width="18.5703125" customWidth="1"/>
+    <col min="52" max="52" width="14.140625" customWidth="1"/>
+    <col min="53" max="53" width="19.42578125" customWidth="1"/>
+    <col min="54" max="54" width="7.140625" customWidth="1"/>
+    <col min="55" max="55" width="12.28515625" customWidth="1"/>
     <col min="56" max="56" width="8" customWidth="1"/>
-    <col min="57" max="57" width="13.33203125" customWidth="1"/>
-    <col min="58" max="58" width="9.5546875" customWidth="1"/>
-    <col min="59" max="59" width="9.6640625" customWidth="1"/>
-    <col min="60" max="60" width="7.21875" customWidth="1"/>
-    <col min="61" max="61" width="9.6640625" customWidth="1"/>
-    <col min="62" max="62" width="8.88671875" customWidth="1"/>
-    <col min="63" max="63" width="11.44140625" customWidth="1"/>
-    <col min="64" max="64" width="9.21875" customWidth="1"/>
-    <col min="65" max="65" width="10.5546875" customWidth="1"/>
-    <col min="66" max="66" width="12.33203125" customWidth="1"/>
-    <col min="67" max="67" width="17.5546875" customWidth="1"/>
+    <col min="57" max="57" width="13.28515625" customWidth="1"/>
+    <col min="58" max="58" width="4.42578125" customWidth="1"/>
+    <col min="59" max="59" width="9.7109375" customWidth="1"/>
+    <col min="60" max="60" width="4.42578125" customWidth="1"/>
+    <col min="61" max="61" width="9.7109375" customWidth="1"/>
+    <col min="62" max="62" width="6.140625" customWidth="1"/>
+    <col min="63" max="63" width="11.42578125" customWidth="1"/>
+    <col min="64" max="64" width="5.28515625" customWidth="1"/>
+    <col min="65" max="65" width="10.5703125" customWidth="1"/>
+    <col min="66" max="66" width="12.28515625" customWidth="1"/>
+    <col min="67" max="67" width="17.5703125" customWidth="1"/>
     <col min="68" max="68" width="15" customWidth="1"/>
-    <col min="69" max="69" width="20.33203125" customWidth="1"/>
+    <col min="69" max="69" width="20.28515625" customWidth="1"/>
     <col min="70" max="70" width="8" customWidth="1"/>
-    <col min="71" max="71" width="13.33203125" customWidth="1"/>
-    <col min="72" max="72" width="16.6640625" customWidth="1"/>
+    <col min="71" max="71" width="13.28515625" customWidth="1"/>
+    <col min="72" max="72" width="16.7109375" customWidth="1"/>
     <col min="73" max="73" width="22" customWidth="1"/>
-    <col min="74" max="74" width="9.6640625" customWidth="1"/>
-    <col min="75" max="75" width="10.5546875" customWidth="1"/>
-    <col min="76" max="76" width="14.109375" customWidth="1"/>
-    <col min="77" max="77" width="19.44140625" customWidth="1"/>
-    <col min="78" max="78" width="14.109375" customWidth="1"/>
-    <col min="79" max="79" width="19.44140625" customWidth="1"/>
-    <col min="80" max="80" width="11.44140625" customWidth="1"/>
-    <col min="81" max="81" width="16.6640625" customWidth="1"/>
-    <col min="82" max="82" width="11.44140625" customWidth="1"/>
-    <col min="83" max="83" width="16.6640625" customWidth="1"/>
-    <col min="84" max="84" width="9.5546875" customWidth="1"/>
-    <col min="85" max="86" width="11.44140625" customWidth="1"/>
-    <col min="87" max="87" width="16.6640625" customWidth="1"/>
-    <col min="88" max="88" width="21.109375" customWidth="1"/>
-    <col min="89" max="89" width="26.44140625" customWidth="1"/>
-    <col min="90" max="90" width="9.77734375" customWidth="1"/>
-    <col min="91" max="91" width="10.5546875" customWidth="1"/>
-    <col min="92" max="92" width="8.5546875" customWidth="1"/>
-    <col min="93" max="93" width="9.6640625" customWidth="1"/>
-    <col min="94" max="94" width="9.44140625" customWidth="1"/>
-    <col min="95" max="95" width="10.5546875" customWidth="1"/>
-    <col min="96" max="96" width="9.88671875" customWidth="1"/>
-    <col min="97" max="97" width="10.5546875" customWidth="1"/>
-    <col min="98" max="98" width="7.109375" customWidth="1"/>
-    <col min="99" max="99" width="12.33203125" customWidth="1"/>
-    <col min="100" max="100" width="10.21875" customWidth="1"/>
-    <col min="101" max="101" width="10.5546875" customWidth="1"/>
-    <col min="102" max="102" width="8.5546875" customWidth="1"/>
-    <col min="103" max="103" width="9.6640625" customWidth="1"/>
-    <col min="104" max="104" width="10.88671875" customWidth="1"/>
-    <col min="105" max="105" width="10.5546875" customWidth="1"/>
+    <col min="74" max="74" width="5.28515625" customWidth="1"/>
+    <col min="75" max="75" width="10.5703125" customWidth="1"/>
+    <col min="76" max="76" width="14.140625" customWidth="1"/>
+    <col min="77" max="77" width="19.42578125" customWidth="1"/>
+    <col min="78" max="78" width="14.140625" customWidth="1"/>
+    <col min="79" max="79" width="19.42578125" customWidth="1"/>
+    <col min="80" max="80" width="11.42578125" customWidth="1"/>
+    <col min="81" max="81" width="16.7109375" customWidth="1"/>
+    <col min="82" max="82" width="11.42578125" customWidth="1"/>
+    <col min="83" max="83" width="16.7109375" customWidth="1"/>
+    <col min="84" max="84" width="6.140625" customWidth="1"/>
+    <col min="85" max="85" width="11.42578125" customWidth="1"/>
+    <col min="86" max="86" width="11.42578125" customWidth="1"/>
+    <col min="87" max="87" width="16.7109375" customWidth="1"/>
+    <col min="88" max="88" width="21.140625" customWidth="1"/>
+    <col min="89" max="89" width="26.42578125" customWidth="1"/>
+    <col min="90" max="90" width="5.28515625" customWidth="1"/>
+    <col min="91" max="91" width="10.5703125" customWidth="1"/>
+    <col min="92" max="92" width="4.42578125" customWidth="1"/>
+    <col min="93" max="93" width="9.7109375" customWidth="1"/>
+    <col min="94" max="94" width="5.28515625" customWidth="1"/>
+    <col min="95" max="95" width="10.5703125" customWidth="1"/>
+    <col min="96" max="96" width="5.28515625" customWidth="1"/>
+    <col min="97" max="97" width="10.5703125" customWidth="1"/>
+    <col min="98" max="98" width="7.140625" customWidth="1"/>
+    <col min="99" max="99" width="12.28515625" customWidth="1"/>
+    <col min="100" max="100" width="5.28515625" customWidth="1"/>
+    <col min="101" max="101" width="10.5703125" customWidth="1"/>
+    <col min="102" max="102" width="4.42578125" customWidth="1"/>
+    <col min="103" max="103" width="9.7109375" customWidth="1"/>
+    <col min="104" max="104" width="5.28515625" customWidth="1"/>
+    <col min="105" max="105" width="10.5703125" customWidth="1"/>
     <col min="106" max="106" width="15" customWidth="1"/>
-    <col min="107" max="107" width="20.33203125" customWidth="1"/>
-    <col min="108" max="108" width="14.109375" customWidth="1"/>
-    <col min="109" max="109" width="19.44140625" customWidth="1"/>
-    <col min="110" max="110" width="7.44140625" customWidth="1"/>
-    <col min="111" max="111" width="9.6640625" customWidth="1"/>
-    <col min="112" max="112" width="10.88671875" customWidth="1"/>
-    <col min="113" max="113" width="10.5546875" customWidth="1"/>
-    <col min="114" max="114" width="14.109375" customWidth="1"/>
-    <col min="115" max="115" width="19.44140625" customWidth="1"/>
-    <col min="116" max="116" width="11.109375" customWidth="1"/>
-    <col min="117" max="117" width="11.44140625" customWidth="1"/>
+    <col min="107" max="107" width="20.28515625" customWidth="1"/>
+    <col min="108" max="108" width="14.140625" customWidth="1"/>
+    <col min="109" max="109" width="19.42578125" customWidth="1"/>
+    <col min="110" max="110" width="4.42578125" customWidth="1"/>
+    <col min="111" max="111" width="9.7109375" customWidth="1"/>
+    <col min="112" max="112" width="5.28515625" customWidth="1"/>
+    <col min="113" max="113" width="10.5703125" customWidth="1"/>
+    <col min="114" max="114" width="14.140625" customWidth="1"/>
+    <col min="115" max="115" width="19.42578125" customWidth="1"/>
+    <col min="116" max="116" width="6.140625" customWidth="1"/>
+    <col min="117" max="117" width="11.42578125" customWidth="1"/>
     <col min="118" max="118" width="15" customWidth="1"/>
-    <col min="119" max="119" width="20.33203125" customWidth="1"/>
+    <col min="119" max="119" width="20.28515625" customWidth="1"/>
     <col min="120" max="120" width="15" customWidth="1"/>
-    <col min="121" max="121" width="20.33203125" customWidth="1"/>
-    <col min="122" max="122" width="10.77734375" customWidth="1"/>
-    <col min="123" max="123" width="11.44140625" customWidth="1"/>
-    <col min="124" max="124" width="17.5546875" customWidth="1"/>
-    <col min="125" max="125" width="22.88671875" customWidth="1"/>
-    <col min="126" max="126" width="20.33203125" customWidth="1"/>
-    <col min="127" max="127" width="25.5546875" customWidth="1"/>
-    <col min="128" max="128" width="12.5546875" customWidth="1"/>
-    <col min="129" max="129" width="15.88671875" customWidth="1"/>
-    <col min="130" max="130" width="22.88671875" customWidth="1"/>
-    <col min="131" max="131" width="28.109375" customWidth="1"/>
-    <col min="132" max="132" width="10" customWidth="1"/>
-    <col min="133" max="133" width="11.44140625" customWidth="1"/>
-    <col min="134" max="134" width="12.33203125" customWidth="1"/>
-    <col min="135" max="135" width="17.5546875" customWidth="1"/>
-    <col min="136" max="136" width="11.44140625" customWidth="1"/>
-    <col min="137" max="137" width="16.6640625" customWidth="1"/>
-    <col min="138" max="138" width="9.44140625" customWidth="1"/>
-    <col min="139" max="139" width="12.33203125" customWidth="1"/>
-    <col min="140" max="140" width="17.5546875" customWidth="1"/>
-    <col min="141" max="141" width="22.88671875" customWidth="1"/>
-    <col min="142" max="142" width="28.109375" customWidth="1"/>
-    <col min="143" max="143" width="33.44140625" customWidth="1"/>
-    <col min="144" max="144" width="13.33203125" customWidth="1"/>
-    <col min="145" max="145" width="18.5546875" customWidth="1"/>
+    <col min="121" max="121" width="20.28515625" customWidth="1"/>
+    <col min="122" max="122" width="6.140625" customWidth="1"/>
+    <col min="123" max="123" width="11.42578125" customWidth="1"/>
+    <col min="124" max="124" width="17.5703125" customWidth="1"/>
+    <col min="125" max="125" width="22.85546875" customWidth="1"/>
+    <col min="126" max="126" width="20.28515625" customWidth="1"/>
+    <col min="127" max="127" width="25.5703125" customWidth="1"/>
+    <col min="128" max="128" width="10.5703125" customWidth="1"/>
+    <col min="129" max="129" width="15.85546875" customWidth="1"/>
+    <col min="130" max="130" width="22.85546875" customWidth="1"/>
+    <col min="131" max="131" width="28.140625" customWidth="1"/>
+    <col min="132" max="132" width="6.140625" customWidth="1"/>
+    <col min="133" max="133" width="11.42578125" customWidth="1"/>
+    <col min="134" max="134" width="12.28515625" customWidth="1"/>
+    <col min="135" max="135" width="17.5703125" customWidth="1"/>
+    <col min="136" max="136" width="11.42578125" customWidth="1"/>
+    <col min="137" max="137" width="16.7109375" customWidth="1"/>
+    <col min="138" max="138" width="7.140625" customWidth="1"/>
+    <col min="139" max="139" width="12.28515625" customWidth="1"/>
+    <col min="140" max="140" width="17.5703125" customWidth="1"/>
+    <col min="141" max="141" width="22.85546875" customWidth="1"/>
+    <col min="142" max="142" width="28.140625" customWidth="1"/>
+    <col min="143" max="143" width="33.42578125" customWidth="1"/>
+    <col min="144" max="144" width="13.28515625" customWidth="1"/>
+    <col min="145" max="145" width="18.5703125" customWidth="1"/>
     <col min="146" max="146" width="15" customWidth="1"/>
-    <col min="147" max="148" width="20.33203125" customWidth="1"/>
-    <col min="149" max="149" width="25.5546875" customWidth="1"/>
-    <col min="150" max="150" width="18.5546875" customWidth="1"/>
-    <col min="151" max="151" width="23.88671875" customWidth="1"/>
-    <col min="152" max="152" width="11.44140625" customWidth="1"/>
-    <col min="153" max="153" width="16.6640625" customWidth="1"/>
-    <col min="154" max="154" width="11.44140625" customWidth="1"/>
-    <col min="155" max="155" width="16.6640625" customWidth="1"/>
-    <col min="156" max="156" width="8.33203125" customWidth="1"/>
-    <col min="157" max="157" width="6.77734375" customWidth="1"/>
-    <col min="158" max="158" width="6.5546875" customWidth="1"/>
-    <col min="159" max="159" width="5.44140625" customWidth="1"/>
-    <col min="160" max="160" width="5.33203125" customWidth="1"/>
-    <col min="161" max="161" width="5.109375" customWidth="1"/>
-    <col min="162" max="162" width="7.44140625" customWidth="1"/>
-    <col min="163" max="163" width="6.109375" customWidth="1"/>
-    <col min="164" max="164" width="5.21875" customWidth="1"/>
-    <col min="165" max="165" width="6.21875" customWidth="1"/>
-    <col min="166" max="167" width="5.5546875" customWidth="1"/>
-    <col min="168" max="168" width="13.33203125" customWidth="1"/>
-    <col min="169" max="169" width="14.109375" customWidth="1"/>
-    <col min="170" max="170" width="9.6640625" customWidth="1"/>
+    <col min="147" max="147" width="20.28515625" customWidth="1"/>
+    <col min="148" max="148" width="20.28515625" customWidth="1"/>
+    <col min="149" max="149" width="25.5703125" customWidth="1"/>
+    <col min="150" max="150" width="18.5703125" customWidth="1"/>
+    <col min="151" max="151" width="23.85546875" customWidth="1"/>
+    <col min="152" max="152" width="11.42578125" customWidth="1"/>
+    <col min="153" max="153" width="16.7109375" customWidth="1"/>
+    <col min="154" max="154" width="11.42578125" customWidth="1"/>
+    <col min="155" max="155" width="16.7109375" customWidth="1"/>
+    <col min="156" max="156" width="3.5703125" customWidth="1"/>
+    <col min="157" max="157" width="3.5703125" customWidth="1"/>
+    <col min="158" max="158" width="3.5703125" customWidth="1"/>
+    <col min="159" max="159" width="3.5703125" customWidth="1"/>
+    <col min="160" max="160" width="3.5703125" customWidth="1"/>
+    <col min="161" max="161" width="3.5703125" customWidth="1"/>
+    <col min="162" max="162" width="3.5703125" customWidth="1"/>
+    <col min="163" max="163" width="3.5703125" customWidth="1"/>
+    <col min="164" max="164" width="3.5703125" customWidth="1"/>
+    <col min="165" max="165" width="4.42578125" customWidth="1"/>
+    <col min="166" max="166" width="4.42578125" customWidth="1"/>
+    <col min="167" max="167" width="4.42578125" customWidth="1"/>
+    <col min="168" max="168" width="13.28515625" customWidth="1"/>
+    <col min="169" max="169" width="14.140625" customWidth="1"/>
+    <col min="170" max="170" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CR1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>98</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>102</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>103</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>104</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>105</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>106</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>108</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>109</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>110</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>111</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>112</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>113</v>
-      </c>
-      <c r="DL1" t="s">
-        <v>114</v>
-      </c>
-      <c r="DM1" t="s">
-        <v>115</v>
-      </c>
-      <c r="DN1" t="s">
-        <v>116</v>
-      </c>
-      <c r="DO1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>119</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>120</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>121</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>122</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>123</v>
-      </c>
-      <c r="DV1" t="s">
-        <v>124</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>125</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>126</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>127</v>
-      </c>
-      <c r="DZ1" t="s">
-        <v>128</v>
-      </c>
-      <c r="EA1" t="s">
-        <v>129</v>
-      </c>
-      <c r="EB1" t="s">
-        <v>130</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>131</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>132</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>133</v>
-      </c>
-      <c r="EF1" t="s">
-        <v>134</v>
-      </c>
-      <c r="EG1" t="s">
-        <v>135</v>
-      </c>
-      <c r="EH1" t="s">
-        <v>136</v>
-      </c>
-      <c r="EI1" t="s">
-        <v>137</v>
-      </c>
-      <c r="EJ1" t="s">
-        <v>138</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>139</v>
-      </c>
-      <c r="EL1" t="s">
-        <v>140</v>
-      </c>
-      <c r="EM1" t="s">
-        <v>141</v>
-      </c>
-      <c r="EN1" t="s">
-        <v>142</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>143</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>144</v>
-      </c>
-      <c r="EQ1" t="s">
-        <v>145</v>
-      </c>
-      <c r="ER1" t="s">
-        <v>146</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>147</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>148</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>149</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>150</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>151</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>152</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>153</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>154</v>
-      </c>
-      <c r="FA1" t="s">
-        <v>155</v>
-      </c>
-      <c r="FB1" t="s">
-        <v>156</v>
-      </c>
-      <c r="FC1" t="s">
-        <v>157</v>
-      </c>
-      <c r="FD1" t="s">
-        <v>158</v>
-      </c>
-      <c r="FE1" t="s">
-        <v>159</v>
-      </c>
-      <c r="FF1" t="s">
-        <v>160</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>161</v>
-      </c>
-      <c r="FH1" t="s">
-        <v>162</v>
-      </c>
-      <c r="FI1" t="s">
-        <v>163</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>164</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>165</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>166</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>167</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>168</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>constraint</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>relation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rhs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç Satış</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Mısır (Dane)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Mısır (Dane) Satış</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru) Satış</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Yulaf</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Yulaf Satış</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot) Satış</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Triticale</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Triticale Satış</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot) Satış</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze Satış</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) Satış</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu Satış</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu Satış</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı Satış</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot)</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot) Satış</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot)</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot) Satış</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot)</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot) Satış</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj)</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj) Satış</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot)</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot) Satış</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik)</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik) Satış</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik)</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik) Satış</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Lavanta</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Lavanta Satış</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze Satış</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz)</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz) Satış</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli)</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli) Satış</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Ispanak</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Ispanak Satış</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Maydanoz</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Maydanoz Satış</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Tere</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Tere Satış</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Nane</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Nane Satış</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Karpuz</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Karpuz Satış</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Kavun</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Kavun Satış</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Biber (Sivri)</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Biber (Sivri) Satış</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık)</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık) Satış</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Patlıcan</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Patlıcan Satış</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık)</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık) Satış</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Havuç</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Havuç Satış</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru)</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru) Satış</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze)</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze) Satış</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru)</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru) Satış</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Soğan (Taze)</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>Soğan (Taze) Satış</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>Pırasa</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>Pırasa Satış</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz)</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz) Satış</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş)</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş) Satış</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>Armut</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>Armut Satış</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>Ayva</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>Ayva Satış</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>Kiraz</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>Kiraz Satış</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>Vişne</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>Vişne Satış</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>Şeftali</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>Şeftali Satış</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>Çilek</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>Çilek Satış</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>Erik</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>Erik Satış</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>Ceviz</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>Ceviz Satış</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu Satış</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür)</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür) Satış</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>Acur</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>Acur Satış</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>Badem</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>Badem Satış</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu)</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu) Satış</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>Çavdar</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>Çavdar Satış</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu Satış</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik)</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik) Satış</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>Kayısı</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>Kayısı Satış</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş Satış</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil)</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil) Satış</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru Satış</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli Satış</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>Sorgum</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>Sorgum Satış</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>Tatlı Patates</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>Tatlı Patates Satış</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu Satış</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>Zerdali</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>Zerdali Satış</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu)</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu)</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru)</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru) Satış</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu)</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil)</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil) Satış</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu)</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu)</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu)</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu) Satış</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>İg1</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>İg2</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>İg3</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>İg4</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>İg5</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>İg6</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>İg7</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>İg8</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>İg9</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>İg10</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>İg11</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>İg12</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>Sermaye Temini</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>Süt sığırcılığı</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>Koyunculuk</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Toplam Arazi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C2">
         <v>5508331</v>
       </c>
       <c r="D2">
@@ -4004,14 +3580,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Toplam Kuru Tarla Arazisi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C3">
         <v>2660003</v>
       </c>
       <c r="D3">
@@ -4516,14 +4096,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="2">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Toplam Sulu Tarla Arazisi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>1013373</v>
       </c>
       <c r="D4">
@@ -5028,14 +4612,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="2">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Toplam Meyve Arazisi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C5">
         <v>154013</v>
       </c>
       <c r="D5">
@@ -5540,14 +5128,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="2">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Toplam Sebze Arazisi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C6">
         <v>397158</v>
       </c>
       <c r="D6">
@@ -6052,14 +5644,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="2">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Toplam Örtü Altı Arazisi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C7">
         <v>4.8</v>
       </c>
       <c r="D7">
@@ -6564,12 +6160,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>173</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Toplam Süs Bitkisi Arazisi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7076,12 +6676,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" t="s">
-        <v>173</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç Arazisi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C9">
         <v>2189475</v>
@@ -7588,12 +7192,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" t="s">
-        <v>173</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C10">
         <v>279382.5</v>
@@ -7604,7 +7212,7 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
@@ -8100,29 +7708,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" t="s">
-        <v>173</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mısır (Dane) Arazisi</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C11">
         <v>13156.5</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
@@ -8137,7 +7749,7 @@
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
@@ -8365,7 +7977,7 @@
       <c r="CJ11">
         <v>0</v>
       </c>
-      <c r="CK11" s="3">
+      <c r="CK11">
         <v>0</v>
       </c>
       <c r="CL11">
@@ -8612,12 +8224,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>173</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru) Arazisi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C12">
         <v>1359679.5</v>
@@ -8628,7 +8244,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
@@ -9124,12 +8740,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" t="s">
-        <v>173</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C13">
         <v>87864</v>
@@ -9636,12 +9256,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" t="s">
-        <v>173</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yulaf Arazisi</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C14">
         <v>28324.5</v>
@@ -10148,12 +9772,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B15" t="s">
-        <v>173</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C15">
         <v>35854.5</v>
@@ -10660,12 +10288,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" t="s">
-        <v>173</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triticale Arazisi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C16">
         <v>31813.5</v>
@@ -11172,12 +10804,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B17" t="s">
-        <v>173</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C17">
         <v>550</v>
@@ -11684,12 +11320,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" t="s">
-        <v>173</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze Arazisi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C18">
         <v>1962</v>
@@ -12196,12 +11836,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" t="s">
-        <v>173</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) Arazisi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C19">
         <v>5076</v>
@@ -12708,15 +12352,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B20" t="s">
-        <v>173</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu Arazisi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C20">
-        <v>72.600000000000009</v>
+        <v>72.60000000000001</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -13220,12 +12868,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B21" t="s">
-        <v>173</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu Arazisi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C21">
         <v>17860.7</v>
@@ -13732,12 +13384,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" t="s">
-        <v>173</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı Arazisi</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C22">
         <v>207465</v>
@@ -14244,12 +13900,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" t="s">
-        <v>173</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C23">
         <v>113121</v>
@@ -14756,12 +14416,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" t="s">
-        <v>173</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C24">
         <v>24649.9</v>
@@ -15268,12 +14932,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B25" t="s">
-        <v>173</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C25">
         <v>66</v>
@@ -15780,12 +15448,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" t="s">
-        <v>173</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj) Arazisi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C26">
         <v>116017.5</v>
@@ -16292,12 +15964,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" t="s">
-        <v>173</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot) Arazisi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C27">
         <v>25470.5</v>
@@ -16804,12 +16480,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik) Arazisi</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C28">
         <v>4867.5</v>
@@ -17316,12 +16996,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" t="s">
-        <v>173</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik) Arazisi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C29">
         <v>30.8</v>
@@ -17828,12 +17512,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" t="s">
-        <v>173</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lavanta Arazisi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C30">
         <v>27.3</v>
@@ -18340,12 +18028,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>202</v>
-      </c>
-      <c r="B31" t="s">
-        <v>173</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze Arazisi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C31">
         <v>2</v>
@@ -18852,12 +18544,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32" t="s">
-        <v>173</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz) Arazisi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C32">
         <v>160.6</v>
@@ -19364,12 +19060,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>204</v>
-      </c>
-      <c r="B33" t="s">
-        <v>173</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli) Arazisi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C33">
         <v>186</v>
@@ -19876,12 +19576,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>205</v>
-      </c>
-      <c r="B34" t="s">
-        <v>173</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ispanak Arazisi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C34">
         <v>258</v>
@@ -20388,12 +20092,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>206</v>
-      </c>
-      <c r="B35" t="s">
-        <v>173</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Maydanoz Arazisi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C35">
         <v>62.4</v>
@@ -20900,12 +20608,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" t="s">
-        <v>173</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tere Arazisi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C36">
         <v>14.4</v>
@@ -21412,12 +21124,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>208</v>
-      </c>
-      <c r="B37" t="s">
-        <v>173</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nane Arazisi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C37">
         <v>6</v>
@@ -21924,12 +21640,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>209</v>
-      </c>
-      <c r="B38" t="s">
-        <v>173</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Karpuz Arazisi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C38">
         <v>4992</v>
@@ -22436,12 +22156,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>210</v>
-      </c>
-      <c r="B39" t="s">
-        <v>173</v>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kavun Arazisi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C39">
         <v>1614</v>
@@ -22948,15 +22672,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>211</v>
-      </c>
-      <c r="B40" t="s">
-        <v>173</v>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biber (Sivri) Arazisi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C40">
-        <v>922.90000000000009</v>
+        <v>922.9000000000001</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -23460,15 +23188,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>212</v>
-      </c>
-      <c r="B41" t="s">
-        <v>173</v>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık) Arazisi</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C41">
-        <v>1101.0999999999999</v>
+        <v>1101.1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -23972,15 +23704,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>213</v>
-      </c>
-      <c r="B42" t="s">
-        <v>173</v>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Patlıcan Arazisi</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C42">
-        <v>957.00000000000011</v>
+        <v>957.0000000000001</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -24484,12 +24220,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>214</v>
-      </c>
-      <c r="B43" t="s">
-        <v>173</v>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık) Arazisi</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C43">
         <v>12311.2</v>
@@ -24996,12 +24736,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>215</v>
-      </c>
-      <c r="B44" t="s">
-        <v>173</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Havuç Arazisi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C44">
         <v>22</v>
@@ -25508,12 +25252,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>216</v>
-      </c>
-      <c r="B45" t="s">
-        <v>173</v>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru) Arazisi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C45">
         <v>189.8</v>
@@ -26020,15 +25768,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>217</v>
-      </c>
-      <c r="B46" t="s">
-        <v>173</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze) Arazisi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C46">
-        <v>131.30000000000001</v>
+        <v>131.3</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -26532,15 +26284,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>218</v>
-      </c>
-      <c r="B47" t="s">
-        <v>173</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru) Arazisi</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C47">
-        <v>605.80000000000007</v>
+        <v>605.8000000000001</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -27044,12 +26800,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>219</v>
-      </c>
-      <c r="B48" t="s">
-        <v>173</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Soğan (Taze) Arazisi</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C48">
         <v>536.9</v>
@@ -27556,12 +27316,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>220</v>
-      </c>
-      <c r="B49" t="s">
-        <v>173</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pırasa Arazisi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C49">
         <v>146.9</v>
@@ -28068,12 +27832,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>221</v>
-      </c>
-      <c r="B50" t="s">
-        <v>173</v>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz) Arazisi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C50">
         <v>37</v>
@@ -28580,12 +28348,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>222</v>
-      </c>
-      <c r="B51" t="s">
-        <v>173</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş) Arazisi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C51">
         <v>72783</v>
@@ -29092,12 +28864,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>223</v>
-      </c>
-      <c r="B52" t="s">
-        <v>173</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Armut Arazisi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C52">
         <v>686</v>
@@ -29604,12 +29380,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>224</v>
-      </c>
-      <c r="B53" t="s">
-        <v>173</v>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ayva Arazisi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C53">
         <v>1</v>
@@ -30116,12 +29896,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" t="s">
-        <v>173</v>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Kiraz Arazisi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C54">
         <v>743</v>
@@ -30628,12 +30412,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>226</v>
-      </c>
-      <c r="B55" t="s">
-        <v>173</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vişne Arazisi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C55">
         <v>172</v>
@@ -31140,12 +30928,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>227</v>
-      </c>
-      <c r="B56" t="s">
-        <v>173</v>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Şeftali Arazisi</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C56">
         <v>250</v>
@@ -31652,12 +31444,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>228</v>
-      </c>
-      <c r="B57" t="s">
-        <v>173</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Çilek Arazisi</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C57">
         <v>685</v>
@@ -32164,12 +31960,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>229</v>
-      </c>
-      <c r="B58" t="s">
-        <v>173</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Erik Arazisi</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C58">
         <v>125</v>
@@ -32676,12 +32476,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>230</v>
-      </c>
-      <c r="B59" t="s">
-        <v>173</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ceviz Arazisi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C59">
         <v>3441</v>
@@ -33188,15 +32992,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>231</v>
-      </c>
-      <c r="B60" t="s">
-        <v>173</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu Arazisi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C60">
-        <v>440.00000000000011</v>
+        <v>440.0000000000001</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -33700,12 +33508,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>232</v>
-      </c>
-      <c r="B61" t="s">
-        <v>173</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür) Arazisi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C61">
         <v>4.8</v>
@@ -34212,12 +34024,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>233</v>
-      </c>
-      <c r="B62" t="s">
-        <v>173</v>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Acur Arazisi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C62">
         <v>11</v>
@@ -34724,12 +34540,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>234</v>
-      </c>
-      <c r="B63" t="s">
-        <v>173</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Badem Arazisi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C63">
         <v>1804</v>
@@ -35236,12 +35056,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>235</v>
-      </c>
-      <c r="B64" t="s">
-        <v>173</v>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C64">
         <v>421.3</v>
@@ -35748,12 +35572,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>236</v>
-      </c>
-      <c r="B65" t="s">
-        <v>173</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Çavdar Arazisi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C65">
         <v>165577.5</v>
@@ -36260,12 +36088,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>237</v>
-      </c>
-      <c r="B66" t="s">
-        <v>173</v>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu Arazisi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C66">
         <v>1800</v>
@@ -36772,12 +36604,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>238</v>
-      </c>
-      <c r="B67" t="s">
-        <v>173</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik) Arazisi</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C67">
         <v>559290</v>
@@ -37284,12 +37120,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>239</v>
-      </c>
-      <c r="B68" t="s">
-        <v>173</v>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kayısı Arazisi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C68">
         <v>6399</v>
@@ -37796,12 +37636,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>240</v>
-      </c>
-      <c r="B69" t="s">
-        <v>173</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş Arazisi</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C69">
         <v>3630</v>
@@ -38308,12 +38152,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>241</v>
-      </c>
-      <c r="B70" t="s">
-        <v>173</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil) Arazisi</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C70">
         <v>3278.6</v>
@@ -38820,12 +38668,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>242</v>
-      </c>
-      <c r="B71" t="s">
-        <v>173</v>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru Arazisi</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C71">
         <v>152080.5</v>
@@ -39332,12 +39184,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>243</v>
-      </c>
-      <c r="B72" t="s">
-        <v>173</v>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli Arazisi</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C72">
         <v>63194</v>
@@ -39844,12 +39700,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>244</v>
-      </c>
-      <c r="B73" t="s">
-        <v>173</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sorgum Arazisi</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C73">
         <v>19.5</v>
@@ -40356,17 +40216,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>245</v>
-      </c>
-      <c r="B74" t="s">
-        <v>173</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tatlı Patates Arazisi</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C74">
         <v>176.07</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
@@ -40868,12 +40732,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>246</v>
-      </c>
-      <c r="B75" t="s">
-        <v>173</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu Arazisi</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C75">
         <v>121915.2</v>
@@ -41380,12 +41248,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>247</v>
-      </c>
-      <c r="B76" t="s">
-        <v>173</v>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Zerdali Arazisi</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C76">
         <v>30</v>
@@ -41892,12 +41764,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>248</v>
-      </c>
-      <c r="B77" t="s">
-        <v>173</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C77">
         <v>1342</v>
@@ -42404,12 +42280,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>249</v>
-      </c>
-      <c r="B78" t="s">
-        <v>173</v>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C78">
         <v>170789</v>
@@ -42916,15 +42796,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>250</v>
-      </c>
-      <c r="B79" t="s">
-        <v>173</v>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru) Arazisi</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C79">
-        <v>4123.6000000000004</v>
+        <v>4123.6</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -43428,12 +43312,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>251</v>
-      </c>
-      <c r="B80" t="s">
-        <v>173</v>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C80">
         <v>4599</v>
@@ -43940,15 +43828,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>252</v>
-      </c>
-      <c r="B81" t="s">
-        <v>173</v>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil) Arazisi</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C81">
-        <v>33.799999999999997</v>
+        <v>33.8</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -44452,12 +44344,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>253</v>
-      </c>
-      <c r="B82" t="s">
-        <v>173</v>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C82">
         <v>42550.3</v>
@@ -44964,12 +44860,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>254</v>
-      </c>
-      <c r="B83" t="s">
-        <v>173</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C83">
         <v>5968.5</v>
@@ -45476,12 +45376,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>255</v>
-      </c>
-      <c r="B84" t="s">
-        <v>173</v>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu) Arazisi</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C84">
         <v>2551.9</v>
@@ -45936,10 +45840,10 @@
       <c r="EW84">
         <v>0</v>
       </c>
-      <c r="EX84" s="3">
+      <c r="EX84">
         <v>1</v>
       </c>
-      <c r="EY84" s="3">
+      <c r="EY84">
         <v>0</v>
       </c>
       <c r="EZ84">
@@ -45988,12 +45892,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>256</v>
-      </c>
-      <c r="B85" t="s">
-        <v>173</v>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Buğday, Durum Buğdayı Hariç Transfer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C85">
         <v>0</v>
@@ -46500,12 +46408,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>257</v>
-      </c>
-      <c r="B86" t="s">
-        <v>173</v>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Buğday (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C86">
         <v>0</v>
@@ -47012,12 +46924,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>258</v>
-      </c>
-      <c r="B87" t="s">
-        <v>173</v>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mısır (Dane) Transfer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C87">
         <v>0</v>
@@ -47524,12 +47440,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>259</v>
-      </c>
-      <c r="B88" t="s">
-        <v>173</v>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Arpa (Diğer) (Kuru) Transfer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C88">
         <v>0</v>
@@ -48036,12 +47956,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>260</v>
-      </c>
-      <c r="B89" t="s">
-        <v>173</v>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Arpa (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C89">
         <v>0</v>
@@ -48548,12 +48472,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>261</v>
-      </c>
-      <c r="B90" t="s">
-        <v>173</v>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Yulaf Transfer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C90">
         <v>0</v>
@@ -49060,12 +48988,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>262</v>
-      </c>
-      <c r="B91" t="s">
-        <v>173</v>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Yulaf (Yeşilot) Transfer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C91">
         <v>0</v>
@@ -49572,12 +49504,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>263</v>
-      </c>
-      <c r="B92" t="s">
-        <v>173</v>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Triticale Transfer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C92">
         <v>0</v>
@@ -50084,12 +50020,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>264</v>
-      </c>
-      <c r="B93" t="s">
-        <v>173</v>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Triticale (Yeşilot) Transfer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C93">
         <v>0</v>
@@ -50596,12 +50536,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>265</v>
-      </c>
-      <c r="B94" t="s">
-        <v>173</v>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fasulye, Taze Transfer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C94">
         <v>0</v>
@@ -51108,12 +51052,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>266</v>
-      </c>
-      <c r="B95" t="s">
-        <v>173</v>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) Transfer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C95">
         <v>0</v>
@@ -51620,12 +51568,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>267</v>
-      </c>
-      <c r="B96" t="s">
-        <v>173</v>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kenevir Tohumu Transfer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C96">
         <v>0</v>
@@ -52132,12 +52084,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>268</v>
-      </c>
-      <c r="B97" t="s">
-        <v>173</v>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu Transfer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C97">
         <v>0</v>
@@ -52644,12 +52600,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>269</v>
-      </c>
-      <c r="B98" t="s">
-        <v>173</v>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Şeker Pancarı Transfer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C98">
         <v>0</v>
@@ -53156,12 +53116,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>270</v>
-      </c>
-      <c r="B99" t="s">
-        <v>173</v>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) (Yeşil Ot) Transfer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C99">
         <v>0</v>
@@ -53668,12 +53632,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>271</v>
-      </c>
-      <c r="B100" t="s">
-        <v>173</v>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Korunga (Yeşilot) Transfer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C100">
         <v>0</v>
@@ -54180,12 +54148,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>272</v>
-      </c>
-      <c r="B101" t="s">
-        <v>173</v>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sorgum (Yeşilot) Transfer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C101">
         <v>0</v>
@@ -54692,12 +54664,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>273</v>
-      </c>
-      <c r="B102" t="s">
-        <v>173</v>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Mısır (Slaj) Transfer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C102">
         <v>0</v>
@@ -55204,12 +55180,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>274</v>
-      </c>
-      <c r="B103" t="s">
-        <v>173</v>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Çayır Otu (Yeşilot) Transfer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C103">
         <v>0</v>
@@ -55716,12 +55696,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>275</v>
-      </c>
-      <c r="B104" t="s">
-        <v>173</v>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Bezelye (Yemlik) Transfer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C104">
         <v>0</v>
@@ -56228,12 +56212,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>276</v>
-      </c>
-      <c r="B105" t="s">
-        <v>173</v>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>İtalyan Çimi (Yemlik) Transfer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C105">
         <v>0</v>
@@ -56740,12 +56728,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>277</v>
-      </c>
-      <c r="B106" t="s">
-        <v>173</v>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Lavanta Transfer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C106">
         <v>0</v>
@@ -57252,12 +57244,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>278</v>
-      </c>
-      <c r="B107" t="s">
-        <v>173</v>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Barbunya, Taze Transfer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C107">
         <v>0</v>
@@ -57764,12 +57760,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>279</v>
-      </c>
-      <c r="B108" t="s">
-        <v>173</v>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Lahana (Beyaz) Transfer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C108">
         <v>0</v>
@@ -58276,12 +58276,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>280</v>
-      </c>
-      <c r="B109" t="s">
-        <v>173</v>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Marul (Göbekli) Transfer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C109">
         <v>0</v>
@@ -58788,12 +58792,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>281</v>
-      </c>
-      <c r="B110" t="s">
-        <v>173</v>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ispanak Transfer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C110">
         <v>0</v>
@@ -59300,12 +59308,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>282</v>
-      </c>
-      <c r="B111" t="s">
-        <v>173</v>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Maydanoz Transfer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C111">
         <v>0</v>
@@ -59812,12 +59824,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>283</v>
-      </c>
-      <c r="B112" t="s">
-        <v>173</v>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tere Transfer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C112">
         <v>0</v>
@@ -60324,12 +60340,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>284</v>
-      </c>
-      <c r="B113" t="s">
-        <v>173</v>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Nane Transfer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C113">
         <v>0</v>
@@ -60836,12 +60856,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>285</v>
-      </c>
-      <c r="B114" t="s">
-        <v>173</v>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Karpuz Transfer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C114">
         <v>0</v>
@@ -61348,12 +61372,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>286</v>
-      </c>
-      <c r="B115" t="s">
-        <v>173</v>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kavun Transfer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C115">
         <v>0</v>
@@ -61860,12 +61888,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>287</v>
-      </c>
-      <c r="B116" t="s">
-        <v>173</v>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Biber (Sivri) Transfer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C116">
         <v>0</v>
@@ -62372,12 +62404,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>288</v>
-      </c>
-      <c r="B117" t="s">
-        <v>173</v>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Hıyar (Sofralık) Transfer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C117">
         <v>0</v>
@@ -62884,12 +62920,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>289</v>
-      </c>
-      <c r="B118" t="s">
-        <v>173</v>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Patlıcan Transfer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C118">
         <v>0</v>
@@ -63396,12 +63436,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>290</v>
-      </c>
-      <c r="B119" t="s">
-        <v>173</v>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Domates (Sofralık) Transfer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C119">
         <v>0</v>
@@ -63908,12 +63952,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>291</v>
-      </c>
-      <c r="B120" t="s">
-        <v>173</v>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Havuç Transfer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C120">
         <v>0</v>
@@ -64420,12 +64468,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>292</v>
-      </c>
-      <c r="B121" t="s">
-        <v>173</v>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sarımsak (Kuru) Transfer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C121">
         <v>0</v>
@@ -64932,12 +64984,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>293</v>
-      </c>
-      <c r="B122" t="s">
-        <v>173</v>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sarımsak (Taze) Transfer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C122">
         <v>0</v>
@@ -65444,12 +65500,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>294</v>
-      </c>
-      <c r="B123" t="s">
-        <v>173</v>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Soğan (Kuru) Transfer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C123">
         <v>0</v>
@@ -65956,12 +66016,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>295</v>
-      </c>
-      <c r="B124" t="s">
-        <v>173</v>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Soğan (Taze) Transfer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C124">
         <v>0</v>
@@ -66468,12 +66532,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>296</v>
-      </c>
-      <c r="B125" t="s">
-        <v>173</v>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Pırasa Transfer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C125">
         <v>0</v>
@@ -66980,12 +67048,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>297</v>
-      </c>
-      <c r="B126" t="s">
-        <v>173</v>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Turp (Beyaz) Transfer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C126">
         <v>0</v>
@@ -67492,12 +67564,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>298</v>
-      </c>
-      <c r="B127" t="s">
-        <v>173</v>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Elma (Bütünleştirilmiş) Transfer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C127">
         <v>0</v>
@@ -68004,12 +68080,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>299</v>
-      </c>
-      <c r="B128" t="s">
-        <v>173</v>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Armut Transfer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C128">
         <v>0</v>
@@ -68516,12 +68596,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>300</v>
-      </c>
-      <c r="B129" t="s">
-        <v>173</v>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ayva Transfer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C129">
         <v>0</v>
@@ -69028,12 +69112,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>301</v>
-      </c>
-      <c r="B130" t="s">
-        <v>173</v>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kiraz Transfer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C130">
         <v>0</v>
@@ -69540,12 +69628,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>302</v>
-      </c>
-      <c r="B131" t="s">
-        <v>173</v>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Vişne Transfer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C131">
         <v>0</v>
@@ -70052,12 +70144,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>303</v>
-      </c>
-      <c r="B132" t="s">
-        <v>173</v>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Şeftali Transfer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C132">
         <v>0</v>
@@ -70564,12 +70660,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>304</v>
-      </c>
-      <c r="B133" t="s">
-        <v>173</v>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Çilek Transfer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C133">
         <v>0</v>
@@ -71076,12 +71176,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>305</v>
-      </c>
-      <c r="B134" t="s">
-        <v>173</v>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Erik Transfer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C134">
         <v>0</v>
@@ -71588,12 +71692,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>306</v>
-      </c>
-      <c r="B135" t="s">
-        <v>173</v>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ceviz Transfer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C135">
         <v>0</v>
@@ -72100,12 +72208,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>307</v>
-      </c>
-      <c r="B136" t="s">
-        <v>173</v>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Çörek Otu Tohumu Transfer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C136">
         <v>0</v>
@@ -72612,12 +72724,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>308</v>
-      </c>
-      <c r="B137" t="s">
-        <v>173</v>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Mantar (Kültür) Transfer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C137">
         <v>0</v>
@@ -73124,12 +73240,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>309</v>
-      </c>
-      <c r="B138" t="s">
-        <v>173</v>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Acur Transfer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C138">
         <v>0</v>
@@ -73636,12 +73756,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>310</v>
-      </c>
-      <c r="B139" t="s">
-        <v>173</v>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Badem Transfer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C139">
         <v>0</v>
@@ -74148,12 +74272,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>311</v>
-      </c>
-      <c r="B140" t="s">
-        <v>173</v>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Buy (Çemen Otu) Transfer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C140">
         <v>0</v>
@@ -74660,12 +74788,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>312</v>
-      </c>
-      <c r="B141" t="s">
-        <v>173</v>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Çavdar Transfer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C141">
         <v>0</v>
@@ -75172,12 +75304,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>313</v>
-      </c>
-      <c r="B142" t="s">
-        <v>173</v>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Fiğ (Adi) Tohumu Transfer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C142">
         <v>0</v>
@@ -75684,12 +75820,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>314</v>
-      </c>
-      <c r="B143" t="s">
-        <v>173</v>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kabak (Çerezlik) Transfer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C143">
         <v>0</v>
@@ -76196,12 +76336,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>315</v>
-      </c>
-      <c r="B144" t="s">
-        <v>173</v>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kayısı Transfer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C144">
         <v>0</v>
@@ -76708,12 +76852,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>316</v>
-      </c>
-      <c r="B145" t="s">
-        <v>173</v>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kimyon, İşlenmemiş Transfer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C145">
         <v>0</v>
@@ -77220,12 +77368,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>317</v>
-      </c>
-      <c r="B146" t="s">
-        <v>173</v>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Mercimek, Kuru (Yeşil) Transfer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C146">
         <v>0</v>
@@ -77732,12 +77884,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>318</v>
-      </c>
-      <c r="B147" t="s">
-        <v>173</v>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Nohut, Kuru Transfer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C147">
         <v>0</v>
@@ -78244,12 +78400,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>319</v>
-      </c>
-      <c r="B148" t="s">
-        <v>173</v>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sofralık Üzüm, Çekirdekli Transfer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C148">
         <v>0</v>
@@ -78756,12 +78916,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>320</v>
-      </c>
-      <c r="B149" t="s">
-        <v>173</v>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sorgum Transfer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C149">
         <v>0</v>
@@ -79268,12 +79432,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>321</v>
-      </c>
-      <c r="B150" t="s">
-        <v>173</v>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tatlı Patates Transfer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C150">
         <v>0</v>
@@ -79780,12 +79948,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>322</v>
-      </c>
-      <c r="B151" t="s">
-        <v>173</v>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Yonca Tohumu Transfer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C151">
         <v>0</v>
@@ -80292,12 +80464,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>323</v>
-      </c>
-      <c r="B152" t="s">
-        <v>173</v>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Zerdali Transfer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C152">
         <v>0</v>
@@ -80804,12 +80980,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>324</v>
-      </c>
-      <c r="B153" t="s">
-        <v>173</v>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Aspir Tohumu (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C153">
         <v>0</v>
@@ -81316,12 +81496,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>325</v>
-      </c>
-      <c r="B154" t="s">
-        <v>173</v>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Ayçiçeği Tohumu (Yağlık) (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C154">
         <v>0</v>
@@ -81828,12 +82012,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>326</v>
-      </c>
-      <c r="B155" t="s">
-        <v>173</v>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Fasulye (Kuru) Transfer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C155">
         <v>0</v>
@@ -82340,12 +82528,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>327</v>
-      </c>
-      <c r="B156" t="s">
-        <v>173</v>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Triticale (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C156">
         <v>0</v>
@@ -82852,12 +83044,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>328</v>
-      </c>
-      <c r="B157" t="s">
-        <v>173</v>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Mercimek, Sulu (Yeşil) Transfer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C157">
         <v>0</v>
@@ -83364,12 +83560,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>329</v>
-      </c>
-      <c r="B158" t="s">
-        <v>173</v>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Fasulye, Kuru (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C158">
         <v>0</v>
@@ -83876,12 +84076,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>330</v>
-      </c>
-      <c r="B159" t="s">
-        <v>173</v>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Yulaf (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C159">
         <v>0</v>
@@ -84388,12 +84592,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>331</v>
-      </c>
-      <c r="B160" t="s">
-        <v>173</v>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Nohut (Sulu) Transfer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C160">
         <v>0</v>
@@ -84848,10 +85056,10 @@
       <c r="EW160">
         <v>0</v>
       </c>
-      <c r="EX160" s="3">
+      <c r="EX160">
         <v>-204</v>
       </c>
-      <c r="EY160" s="3">
+      <c r="EY160">
         <v>1</v>
       </c>
       <c r="EZ160">
@@ -84900,12 +85108,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>332</v>
-      </c>
-      <c r="B161" t="s">
-        <v>173</v>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>İşgücü Ocak</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C161">
         <v>28727400</v>
@@ -85412,12 +85624,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>333</v>
-      </c>
-      <c r="B162" t="s">
-        <v>173</v>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>İşgücü Şubat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C162">
         <v>28727400</v>
@@ -85609,13 +85825,13 @@
         <v>0</v>
       </c>
       <c r="BN162">
-        <v>4.3899999999999997</v>
+        <v>4.39</v>
       </c>
       <c r="BO162">
         <v>0</v>
       </c>
       <c r="BP162">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="BQ162">
         <v>0</v>
@@ -85741,7 +85957,7 @@
         <v>0</v>
       </c>
       <c r="DF162">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="DG162">
         <v>0</v>
@@ -85924,12 +86140,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>334</v>
-      </c>
-      <c r="B163" t="s">
-        <v>173</v>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>İşgücü Mart</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C163">
         <v>33796940</v>
@@ -85953,13 +86173,13 @@
         <v>0</v>
       </c>
       <c r="J163">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="K163">
         <v>0</v>
       </c>
       <c r="L163">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="M163">
         <v>0</v>
@@ -86121,13 +86341,13 @@
         <v>0</v>
       </c>
       <c r="BN163">
-        <v>4.3899999999999997</v>
+        <v>4.39</v>
       </c>
       <c r="BO163">
         <v>0</v>
       </c>
       <c r="BP163">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="BQ163">
         <v>0</v>
@@ -86253,7 +86473,7 @@
         <v>0</v>
       </c>
       <c r="DF163">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="DG163">
         <v>0</v>
@@ -86436,12 +86656,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>335</v>
-      </c>
-      <c r="B164" t="s">
-        <v>173</v>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>İşgücü Nisan</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C164">
         <v>45625870</v>
@@ -86633,13 +86857,13 @@
         <v>0</v>
       </c>
       <c r="BN164">
-        <v>4.3899999999999997</v>
+        <v>4.39</v>
       </c>
       <c r="BO164">
         <v>0</v>
       </c>
       <c r="BP164">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="BQ164">
         <v>0</v>
@@ -86747,7 +86971,7 @@
         <v>0</v>
       </c>
       <c r="CZ164">
-        <v>9.8000000000000007</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DA164">
         <v>0</v>
@@ -86765,13 +86989,13 @@
         <v>0</v>
       </c>
       <c r="DF164">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="DG164">
         <v>0</v>
       </c>
       <c r="DH164">
-        <v>9.8000000000000007</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DI164">
         <v>0</v>
@@ -86948,12 +87172,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>336</v>
-      </c>
-      <c r="B165" t="s">
-        <v>173</v>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>İşgücü Mayıs</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C165">
         <v>45625870</v>
@@ -86965,7 +87193,7 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -87460,12 +87688,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>337</v>
-      </c>
-      <c r="B166" t="s">
-        <v>173</v>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>İşgücü Haziran</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C166">
         <v>45625870</v>
@@ -87489,13 +87721,13 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="K166">
         <v>0</v>
       </c>
       <c r="L166">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="M166">
         <v>0</v>
@@ -87771,7 +88003,7 @@
         <v>0</v>
       </c>
       <c r="CZ166">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="DA166">
         <v>0</v>
@@ -87795,7 +88027,7 @@
         <v>0</v>
       </c>
       <c r="DH166">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="DI166">
         <v>0</v>
@@ -87861,7 +88093,7 @@
         <v>0</v>
       </c>
       <c r="ED166">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="EE166">
         <v>0</v>
@@ -87903,13 +88135,13 @@
         <v>0</v>
       </c>
       <c r="ER166">
-        <v>8.6199999999999992</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="ES166">
         <v>0</v>
       </c>
       <c r="ET166">
-        <v>8.6199999999999992</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="EU166">
         <v>0</v>
@@ -87972,12 +88204,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>338</v>
-      </c>
-      <c r="B167" t="s">
-        <v>173</v>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>İşgücü Temmuz</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C167">
         <v>45625870</v>
@@ -88037,7 +88273,7 @@
         <v>0</v>
       </c>
       <c r="V167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="W167">
         <v>0</v>
@@ -88115,7 +88351,7 @@
         <v>0</v>
       </c>
       <c r="AV167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AW167">
         <v>0</v>
@@ -88127,31 +88363,31 @@
         <v>0</v>
       </c>
       <c r="AZ167">
-        <v>68.900000000000006</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="BA167">
         <v>0</v>
       </c>
       <c r="BB167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BC167">
         <v>0</v>
       </c>
       <c r="BD167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BE167">
         <v>0</v>
       </c>
       <c r="BF167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BG167">
         <v>0</v>
       </c>
       <c r="BH167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI167">
         <v>0</v>
@@ -88181,7 +88417,7 @@
         <v>0</v>
       </c>
       <c r="BR167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BS167">
         <v>0</v>
@@ -88205,7 +88441,7 @@
         <v>0</v>
       </c>
       <c r="BZ167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CA167">
         <v>0</v>
@@ -88217,13 +88453,13 @@
         <v>0</v>
       </c>
       <c r="CD167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CE167">
         <v>0</v>
       </c>
       <c r="CF167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CG167">
         <v>0</v>
@@ -88241,49 +88477,49 @@
         <v>0</v>
       </c>
       <c r="CL167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="CM167">
         <v>0</v>
       </c>
       <c r="CN167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="CO167">
         <v>0</v>
       </c>
       <c r="CP167">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CQ167">
         <v>0</v>
       </c>
       <c r="CR167">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CS167">
         <v>0</v>
       </c>
       <c r="CT167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="CU167">
         <v>0</v>
       </c>
       <c r="CV167">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CW167">
         <v>0</v>
       </c>
       <c r="CX167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="CY167">
         <v>0</v>
       </c>
       <c r="CZ167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="DA167">
         <v>0</v>
@@ -88295,7 +88531,7 @@
         <v>0</v>
       </c>
       <c r="DD167">
-        <v>9.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DE167">
         <v>0</v>
@@ -88307,7 +88543,7 @@
         <v>0</v>
       </c>
       <c r="DH167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="DI167">
         <v>0</v>
@@ -88337,7 +88573,7 @@
         <v>0</v>
       </c>
       <c r="DR167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="DS167">
         <v>0</v>
@@ -88349,7 +88585,7 @@
         <v>0</v>
       </c>
       <c r="DV167">
-        <v>9.3800000000000008</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DW167">
         <v>0</v>
@@ -88373,7 +88609,7 @@
         <v>0</v>
       </c>
       <c r="ED167">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="EE167">
         <v>0</v>
@@ -88385,7 +88621,7 @@
         <v>0</v>
       </c>
       <c r="EH167">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="EI167">
         <v>0</v>
@@ -88403,7 +88639,7 @@
         <v>0</v>
       </c>
       <c r="EN167">
-        <v>9.3800000000000008</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="EO167">
         <v>0</v>
@@ -88484,12 +88720,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>339</v>
-      </c>
-      <c r="B168" t="s">
-        <v>173</v>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>İşgücü Ağustos</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C168">
         <v>45625870</v>
@@ -88639,7 +88879,7 @@
         <v>0</v>
       </c>
       <c r="AZ168">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="BA168">
         <v>0</v>
@@ -88753,49 +88993,49 @@
         <v>0</v>
       </c>
       <c r="CL168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="CM168">
         <v>0</v>
       </c>
       <c r="CN168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="CO168">
         <v>0</v>
       </c>
       <c r="CP168">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CQ168">
         <v>0</v>
       </c>
       <c r="CR168">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CS168">
         <v>0</v>
       </c>
       <c r="CT168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="CU168">
         <v>0</v>
       </c>
       <c r="CV168">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CW168">
         <v>0</v>
       </c>
       <c r="CX168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="CY168">
         <v>0</v>
       </c>
       <c r="CZ168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="DA168">
         <v>0</v>
@@ -88819,7 +89059,7 @@
         <v>0</v>
       </c>
       <c r="DH168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="DI168">
         <v>0</v>
@@ -88849,7 +89089,7 @@
         <v>0</v>
       </c>
       <c r="DR168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="DS168">
         <v>0</v>
@@ -88897,7 +89137,7 @@
         <v>0</v>
       </c>
       <c r="EH168">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="EI168">
         <v>0</v>
@@ -88996,12 +89236,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>340</v>
-      </c>
-      <c r="B169" t="s">
-        <v>173</v>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>İşgücü Eylül</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C169">
         <v>45625870</v>
@@ -89396,7 +89640,7 @@
       <c r="EC169">
         <v>0</v>
       </c>
-      <c r="ED169" s="3">
+      <c r="ED169">
         <v>0</v>
       </c>
       <c r="EE169">
@@ -89439,13 +89683,13 @@
         <v>0</v>
       </c>
       <c r="ER169">
-        <v>10.029999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="ES169">
         <v>0</v>
       </c>
       <c r="ET169">
-        <v>10.029999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="EU169">
         <v>0</v>
@@ -89457,7 +89701,7 @@
         <v>0</v>
       </c>
       <c r="EX169">
-        <v>10.029999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="EY169">
         <v>0</v>
@@ -89508,12 +89752,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>341</v>
-      </c>
-      <c r="B170" t="s">
-        <v>173</v>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>İşgücü Ekim</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C170">
         <v>45625870</v>
@@ -89908,7 +90156,7 @@
       <c r="EC170">
         <v>0</v>
       </c>
-      <c r="ED170" s="3">
+      <c r="ED170">
         <v>0</v>
       </c>
       <c r="EE170">
@@ -90020,12 +90268,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>342</v>
-      </c>
-      <c r="B171" t="s">
-        <v>173</v>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>İşgücü Kasım</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C171">
         <v>33796940</v>
@@ -90420,7 +90672,7 @@
       <c r="EC171">
         <v>0</v>
       </c>
-      <c r="ED171" s="3">
+      <c r="ED171">
         <v>0</v>
       </c>
       <c r="EE171">
@@ -90532,12 +90784,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>343</v>
-      </c>
-      <c r="B172" t="s">
-        <v>173</v>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>İşgücü Aralık</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C172">
         <v>28727400</v>
@@ -90932,7 +91188,7 @@
       <c r="EC172">
         <v>0</v>
       </c>
-      <c r="ED172" s="3">
+      <c r="ED172">
         <v>0</v>
       </c>
       <c r="EE172">
@@ -91044,15 +91300,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>344</v>
-      </c>
-      <c r="B173" t="s">
-        <v>173</v>
-      </c>
-      <c r="C173" s="2">
-        <v>10184195908.549999</v>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>İşletme Sermayesi</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>10184195908.55</v>
       </c>
       <c r="D173">
         <v>324.12</v>
@@ -91103,7 +91363,7 @@
         <v>0</v>
       </c>
       <c r="T173">
-        <v>923.56</v>
+        <v>923.5599999999999</v>
       </c>
       <c r="U173">
         <v>0</v>
@@ -91199,7 +91459,7 @@
         <v>0</v>
       </c>
       <c r="AZ173">
-        <v>4564.1400000000003</v>
+        <v>4564.14</v>
       </c>
       <c r="BA173">
         <v>0</v>
@@ -91235,13 +91495,13 @@
         <v>0</v>
       </c>
       <c r="BL173">
-        <v>2166.6799999999998</v>
+        <v>2166.68</v>
       </c>
       <c r="BM173">
         <v>0</v>
       </c>
       <c r="BN173">
-        <v>8502.9500000000007</v>
+        <v>8502.950000000001</v>
       </c>
       <c r="BO173">
         <v>0</v>
@@ -91415,7 +91675,7 @@
         <v>0</v>
       </c>
       <c r="DT173">
-        <v>515.29999999999995</v>
+        <v>515.3</v>
       </c>
       <c r="DU173">
         <v>0</v>
@@ -91556,12 +91816,16 @@
         <v>741</v>
       </c>
     </row>
-    <row r="174" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>345</v>
-      </c>
-      <c r="B174" t="s">
-        <v>173</v>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Ahır Yeri</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C174">
         <v>25736172</v>
@@ -92068,12 +92332,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:170" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>346</v>
-      </c>
-      <c r="B175" t="s">
-        <v>173</v>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Ağıl Yeri</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="C175">
         <v>2735827</v>
@@ -92582,6 +92850,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>